--- a/cloudflare-deploy/public/library/agency/agency-kr.xlsx
+++ b/cloudflare-deploy/public/library/agency/agency-kr.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1862,6 +1862,60 @@
       <c r="E25" s="20" t="inlineStr">
         <is>
           <t>상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>🗂️</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요). → 명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요. → 적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요. → 강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요. → 급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>학부모 월간 성적표 (오각형) 발송</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>월간 리포트 화면을 열어요. → 학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요. → 오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요. → 주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4633,8 +4687,330 @@
       <c r="E247" s="33" t="n"/>
       <c r="F247" s="33" t="n"/>
     </row>
+    <row r="249" ht="26" customHeight="1">
+      <c r="A249" s="21" t="inlineStr">
+        <is>
+          <t>23  🗂️ 강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)  —  찾기 쉬운 명부 · 한눈에 보는 상세</t>
+        </is>
+      </c>
+      <c r="B249" s="22" t="n"/>
+      <c r="C249" s="22" t="n"/>
+      <c r="D249" s="22" t="n"/>
+      <c r="E249" s="22" t="n"/>
+      <c r="F249" s="22" t="n"/>
+    </row>
+    <row r="250" ht="42" customHeight="1">
+      <c r="A250" s="23" t="inlineStr">
+        <is>
+          <t>📖 강사 관리 화면이 찾기 쉽고 보기 편하게 정리됐어요. 흩어져 있던 메뉴를 네 묶음으로 그룹지어 사이드바에 담았고, 강사 명부 위에는 구분·상태·그룹 드롭다운 필터와 적용된 필터 칩이 생겼어요. 강사를 누르면 프로필·급여·평가 탭으로 나뉜 상세 화면이 열리고, 매니저 배지와 재직 상태(재직·휴직·퇴사) 가 한눈에 표시돼요.</t>
+        </is>
+      </c>
+      <c r="B250" s="24" t="n"/>
+      <c r="C250" s="24" t="n"/>
+      <c r="D250" s="24" t="n"/>
+      <c r="E250" s="24" t="n"/>
+      <c r="F250" s="24" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B251" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="30" customHeight="1">
+      <c r="A252" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B252" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="30" customHeight="1">
+      <c r="A253" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B253" s="28" t="inlineStr">
+        <is>
+          <t>명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="30" customHeight="1">
+      <c r="A254" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B254" s="28" t="inlineStr">
+        <is>
+          <t>적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="30" customHeight="1">
+      <c r="A255" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B255" s="28" t="inlineStr">
+        <is>
+          <t>강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="30" customHeight="1">
+      <c r="A256" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B256" s="28" t="inlineStr">
+        <is>
+          <t>급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="24" customHeight="1">
+      <c r="A257" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B257" s="30" t="inlineStr">
+        <is>
+          <t>매니저는 배지로 구분되고, 재직 상태가 재직·휴직·퇴사 3가지로 표시돼요.</t>
+        </is>
+      </c>
+      <c r="C257" s="31" t="n"/>
+      <c r="D257" s="31" t="n"/>
+      <c r="E257" s="31" t="n"/>
+      <c r="F257" s="31" t="n"/>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B258" s="30" t="inlineStr">
+        <is>
+          <t>이름이 비어도 아이디로 대체 표기돼 빈칸이 없어요.</t>
+        </is>
+      </c>
+      <c r="C258" s="31" t="n"/>
+      <c r="D258" s="31" t="n"/>
+      <c r="E258" s="31" t="n"/>
+      <c r="F258" s="31" t="n"/>
+    </row>
+    <row r="259" ht="24" customHeight="1">
+      <c r="A259" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B259" s="30" t="inlineStr">
+        <is>
+          <t>상세 탭은 기존 API를 재사용해 빠르게 뜨고, 화면은 한/영 병기예요.</t>
+        </is>
+      </c>
+      <c r="C259" s="31" t="n"/>
+      <c r="D259" s="31" t="n"/>
+      <c r="E259" s="31" t="n"/>
+      <c r="F259" s="31" t="n"/>
+    </row>
+    <row r="260" ht="24" customHeight="1">
+      <c r="A260" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B260" s="30" t="inlineStr">
+        <is>
+          <t>중복이던 급여 입구를 정리하고 버그 접수는 별도 시스템으로 옮겼어요.</t>
+        </is>
+      </c>
+      <c r="C260" s="31" t="n"/>
+      <c r="D260" s="31" t="n"/>
+      <c r="E260" s="31" t="n"/>
+      <c r="F260" s="31" t="n"/>
+    </row>
+    <row r="261" ht="26" customHeight="1">
+      <c r="A261" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
+        </is>
+      </c>
+      <c r="B261" s="35" t="n"/>
+      <c r="C261" s="35" t="n"/>
+      <c r="D261" s="35" t="n"/>
+      <c r="E261" s="35" t="n"/>
+      <c r="F261" s="35" t="n"/>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+      <c r="B262" s="33" t="n"/>
+      <c r="C262" s="33" t="n"/>
+      <c r="D262" s="33" t="n"/>
+      <c r="E262" s="33" t="n"/>
+      <c r="F262" s="33" t="n"/>
+    </row>
+    <row r="264" ht="26" customHeight="1">
+      <c r="A264" s="21" t="inlineStr">
+        <is>
+          <t>24  🌟 학부모 월간 성적표 (오각형) 발송  —  5축 그래프 성적표를 미리보고 링크로</t>
+        </is>
+      </c>
+      <c r="B264" s="22" t="n"/>
+      <c r="C264" s="22" t="n"/>
+      <c r="D264" s="22" t="n"/>
+      <c r="E264" s="22" t="n"/>
+      <c r="F264" s="22" t="n"/>
+    </row>
+    <row r="265" ht="42" customHeight="1">
+      <c r="A265" s="23" t="inlineStr">
+        <is>
+          <t>📖 학부모에게 보내는 월간 성적표가 오각형 5축 그래프로 새로워졌어요. 발음·유창성 / 어휘 / 문장 구성력 / 수업 태도 / 참여도 를 한눈에 보여 주고, 출결·판단력·담임의 한마디가 함께 담깁니다. 관리자·교사는 학생 ID와 월을 넣어 미리보기한 뒤 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="B265" s="24" t="n"/>
+      <c r="C265" s="24" t="n"/>
+      <c r="D265" s="24" t="n"/>
+      <c r="E265" s="24" t="n"/>
+      <c r="F265" s="24" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B266" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="30" customHeight="1">
+      <c r="A267" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B267" s="28" t="inlineStr">
+        <is>
+          <t>월간 리포트 화면을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="30" customHeight="1">
+      <c r="A268" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B268" s="28" t="inlineStr">
+        <is>
+          <t>학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="30" customHeight="1">
+      <c r="A269" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B269" s="28" t="inlineStr">
+        <is>
+          <t>오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="30" customHeight="1">
+      <c r="A270" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="24" customHeight="1">
+      <c r="A271" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B271" s="30" t="inlineStr">
+        <is>
+          <t>실제 기록이 있는 축만 채워져 신뢰할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C271" s="31" t="n"/>
+      <c r="D271" s="31" t="n"/>
+      <c r="E271" s="31" t="n"/>
+      <c r="F271" s="31" t="n"/>
+    </row>
+    <row r="272" ht="24" customHeight="1">
+      <c r="A272" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B272" s="30" t="inlineStr">
+        <is>
+          <t>2개월 주기로 정리해 학부모 피로 없이 변화를 전달해요.</t>
+        </is>
+      </c>
+      <c r="C272" s="31" t="n"/>
+      <c r="D272" s="31" t="n"/>
+      <c r="E272" s="31" t="n"/>
+      <c r="F272" s="31" t="n"/>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B273" s="30" t="inlineStr">
+        <is>
+          <t>인쇄/PDF 버튼으로 상담용 종이 성적표도 즉시 만들 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C273" s="31" t="n"/>
+      <c r="D273" s="31" t="n"/>
+      <c r="E273" s="31" t="n"/>
+      <c r="F273" s="31" t="n"/>
+    </row>
+    <row r="274" ht="26" customHeight="1">
+      <c r="A274" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
+        </is>
+      </c>
+      <c r="B274" s="35" t="n"/>
+      <c r="C274" s="35" t="n"/>
+      <c r="D274" s="35" t="n"/>
+      <c r="E274" s="35" t="n"/>
+      <c r="F274" s="35" t="n"/>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
+        </is>
+      </c>
+      <c r="B275" s="33" t="n"/>
+      <c r="C275" s="33" t="n"/>
+      <c r="D275" s="33" t="n"/>
+      <c r="E275" s="33" t="n"/>
+      <c r="F275" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="225">
+  <mergeCells count="251">
     <mergeCell ref="A174:F174"/>
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
@@ -4642,6 +5018,7 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B81:F81"/>
     <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B252:F252"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="A3:F3"/>
@@ -4654,6 +5031,7 @@
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A150:F150"/>
+    <mergeCell ref="B253:F253"/>
     <mergeCell ref="B231:F231"/>
     <mergeCell ref="A159:F159"/>
     <mergeCell ref="A97:F97"/>
@@ -4664,12 +5042,17 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B166:F166"/>
+    <mergeCell ref="A265:F265"/>
     <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A274:F274"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B116:F116"/>
+    <mergeCell ref="A249:F249"/>
+    <mergeCell ref="B270:F270"/>
     <mergeCell ref="B230:F230"/>
     <mergeCell ref="B168:F168"/>
+    <mergeCell ref="B257:F257"/>
     <mergeCell ref="B84:F84"/>
     <mergeCell ref="B143:F143"/>
     <mergeCell ref="A186:F186"/>
@@ -4687,7 +5070,9 @@
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B256:F256"/>
     <mergeCell ref="B94:F94"/>
+    <mergeCell ref="A250:F250"/>
     <mergeCell ref="B135:F135"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="A99:F99"/>
@@ -4712,10 +5097,13 @@
     <mergeCell ref="B176:F176"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="A262:F262"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B175:F175"/>
+    <mergeCell ref="B266:F266"/>
     <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B267:F267"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="B10:F10"/>
@@ -4724,6 +5112,7 @@
     <mergeCell ref="A127:F127"/>
     <mergeCell ref="B217:F217"/>
     <mergeCell ref="A48:F48"/>
+    <mergeCell ref="B269:F269"/>
     <mergeCell ref="A232:F232"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A59:F59"/>
@@ -4731,6 +5120,7 @@
     <mergeCell ref="B239:F239"/>
     <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B254:F254"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B5:F5"/>
@@ -4741,9 +5131,11 @@
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B216:F216"/>
+    <mergeCell ref="B251:F251"/>
     <mergeCell ref="A162:F162"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="A46:F46"/>
@@ -4757,12 +5149,15 @@
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B202:F202"/>
     <mergeCell ref="B215:F215"/>
+    <mergeCell ref="B273:F273"/>
     <mergeCell ref="A139:F139"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B272:F272"/>
     <mergeCell ref="B244:F244"/>
+    <mergeCell ref="B259:F259"/>
     <mergeCell ref="B136:F136"/>
     <mergeCell ref="B229:F229"/>
     <mergeCell ref="B23:F23"/>
@@ -4777,12 +5172,15 @@
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B243:F243"/>
+    <mergeCell ref="B258:F258"/>
     <mergeCell ref="B178:F178"/>
     <mergeCell ref="A117:F117"/>
     <mergeCell ref="A173:F173"/>
     <mergeCell ref="B245:F245"/>
+    <mergeCell ref="B255:F255"/>
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B260:F260"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="B192:F192"/>
@@ -4806,6 +5204,7 @@
     <mergeCell ref="B91:F91"/>
     <mergeCell ref="A246:F246"/>
     <mergeCell ref="B156:F156"/>
+    <mergeCell ref="A264:F264"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="B165:F165"/>
     <mergeCell ref="A233:F233"/>
@@ -4842,6 +5241,8 @@
     <mergeCell ref="A130:F130"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A261:F261"/>
+    <mergeCell ref="A275:F275"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="A222:F222"/>
     <mergeCell ref="B64:F64"/>
@@ -4858,6 +5259,7 @@
     <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B268:F268"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>

--- a/cloudflare-deploy/public/library/agency/agency-kr.xlsx
+++ b/cloudflare-deploy/public/library/agency/agency-kr.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,12 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00E11D48"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00E11D48"/>
       <sz val="11"/>
     </font>
     <font>
@@ -181,7 +187,7 @@
       <sz val="11.5"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -216,6 +222,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -265,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -331,25 +342,25 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -358,10 +369,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -370,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -379,26 +394,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -410,17 +425,17 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -709,6 +724,786 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="514350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>125</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>149</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2476500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>173</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>186</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="1152525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>213</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>227</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>239</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>252</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>281</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>297</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>311</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>326</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>341</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>354</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>366</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>379</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>392</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4000500" cy="2495550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1227,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1387,7 +2182,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>🧑‍🎓</t>
+          <t>🎓</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -1414,7 +2209,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>👨‍👩‍👧</t>
+          <t>👪</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -1916,6 +2711,195 @@
       <c r="E27" s="20" t="inlineStr">
         <is>
           <t>상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>학부모 주간 리포트 (재등록을 잇는 무기)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 📅 학부모 주간 리포트를 열어요. → 학생 ID를 넣고 미리보기로 내용을 확인해요. → 필요하면 이 학부모에게 실제 발송으로 한 명에게만 테스트해요. → 발송 대상 집계로 지금 받을 수 있는 학생 수(전화번호 등록자)를 확인해요. → 최근 발송 로그로 실제로 나간 기록을 확인해요.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>먼저 미리보기 → 한 명 테스트 발송까지만 해 보세요. 문구가 확정되면 그때 전체 스위치를 켜면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>🏠</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>홈 첫 화면 개편 (처음 온 학부모 · 기존 회원 자동 분리)</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>새 창(시크릿 모드)으로 홈 주소를 열어 비회원 화면을 확인해요. → 무료 체험 신청 · 강사 둘러보기 두 버튼이 크게 보이는지 봐요. → 로그인한 뒤 같은 화면을 열면 수업 입장 · AI와 친구하기로 바뀌어요. → 홍보물·문자에는 홈 주소 그대로 넣으면 됩니다 — 별도 랜딩페이지가 필요 없어요.</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>체험 신청 전환을 보고 싶다면 시크릿 창으로 홈에 들어가 보세요. 학부모가 처음 보는 화면이 그대로 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>관리자 화면이 훨씬 빨라졌어요</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>관리자 화면을 평소처럼 사용해요. → 메뉴·카드를 눌렀을 때 멈춤 없이 바로 열리는지 확인해요. → 느리게 느껴지면 브라우저에서 새로고침(Ctrl+F5) 을 한 번 해 주세요.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>그래도 느리다면 브라우저 탭을 너무 많이 열어 두지 않았는지 확인해 보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>🔎</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>학원 검색칸 (이름으로 바로 찾기)</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 학원 목록 화면을 열어요. → 목록 위 검색칸에 학원 이름 일부를 입력해요. → 입력하는 즉시 해당 학원만 목록에 남아요. → 검색칸을 비우면 전체 목록으로 돌아와요.</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>자주 확인하는 학원이 있다면 이름 두세 글자만 외워 두세요. 클릭 없이 바로 걸러집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>신규 결제 화면 단계형 개편</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>학부모에게 신규 결제 화면을 안내해요. → 대상(키즈·일반 1:1·그룹·비즈니스·시험·기업)을 먼저 고르게 해요. → 고른 대상에 맞는 상품만 화면에 남아요. → 전체를 비교하고 싶어 하면 전체 요금표 보기를 눌러 주세요.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>상담 전화에서 ‘어떤 걸 고를지 모르겠다’는 말이 나오면, 대상만 먼저 고르게 안내하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>📋</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>계정 없는 학부모용 샘플 평가표</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>상담 중 학부모에게 평가표 화면을 열어 보여 줘요. → 계정이 없어요 — 샘플 평가표 먼저 보기를 눌러요. → 5축 점수·강사 코멘트·AI 분석 구성을 함께 보며 설명해요. → ‘우리 아이 것도 이렇게 나옵니다’로 체험 신청을 연결해요.</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>상담 첫 3분에 샘플 평가표를 보여 주면 ‘무엇을 받게 되는지’가 명확해져 체험 전환이 올라갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>📞</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>상담 창구·운영시간 통일 (카카오 1순위)</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>문의하기 화면에서 카드 순서가 카카오 → 전화 인지 확인해요. → 학부모 안내 시 카카오 채널을 먼저 안내해요. → 운영시간은 10:00~23:00 (주말·공휴일 휴무) 로 통일해 안내해요.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>필리핀 콜센터 번호가 필요하면 실번호를 알려 주세요 — 자리표시자였던 번호는 삭제된 상태입니다.</t>
         </is>
       </c>
     </row>
@@ -1933,7 +2917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1942,6 +2926,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1975,3295 +2961,4776 @@
       <c r="E4" s="24" t="n"/>
       <c r="F4" s="24" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>🧭  1 아이디·비밀번호   ›   2 권한(대리점)   ›   3 ‘비밀번호 찾기’</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="27" t="n">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>아이디·비밀번호로 로그인해요. (소셜 로그인도 가능)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="27" t="n">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>로그인하면 권한(대리점) 에 맞는 메뉴·데이터가 자동 적용돼요.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="27" t="n">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>비밀번호를 잊었으면 ‘비밀번호 찾기’로 재설정해요.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>우리 대리점 학생·매출 데이터만 보여요.</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="31" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>안전한 내 PC에서만 ‘아이디 저장’을 켜세요.</t>
         </is>
       </c>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 공용 PC에서는 자동 로그인을 끄고 사용 후 로그아웃하세요.</t>
-        </is>
-      </c>
-      <c r="B11" s="33" t="n"/>
       <c r="C11" s="33" t="n"/>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 공용 PC에서는 자동 로그인을 끄고 사용 후 로그아웃하세요.</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1"/>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>02  👤 마이페이지 &amp; 관리자 대시보드  —  마이페이지에서 관리 화면 열기</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>📖 대리점 운영도 ‘마이페이지’에서 시작해요. 로그인 후 마이페이지의 메뉴 중 📊 ‘관리자’ 버튼을 누르면 우리 대리점 범위의 관리자(운영) 대시보드로 들어가, 학생·매출·수업·정산을 관리할 수 있어요.</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 ‘👤 마이페이지’   ›   2 📊 ‘관리자’   ›   3 관리자 대시보드   ›   4 마이페이지에는 연기/변경…   ›   5 EN</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="27" t="n">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>로그인 후 화면에서 ‘👤 마이페이지’를 열어요.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="27" t="n">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>마이페이지 메뉴에서 📊 ‘관리자’ 버튼을 눌러요. (관리자 대시보드로 이동)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="27" t="n">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>관리자 대시보드에서 우리 대리점 매출·재원·오늘 수업을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="27" t="n">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>마이페이지에는 연기/변경·신규상담·전체메뉴·수업 진단 등도 함께 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="27" t="n">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>글자가 영어로 보이면 EN 버튼으로 한국어로 바꿔요.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>‘관리자’ 버튼 하나로 바로 운영 대시보드에 들어가요.</t>
         </is>
       </c>
-      <c r="C21" s="31" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>대시보드 데이터는 모두 ‘우리 대리점 범위’로 자동 집계돼요.</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>권한(대리점)에 따라 보이는 메뉴·데이터가 자동으로 정해져요.</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 마이페이지·관리자 대시보드 모두 로그인한 대리점 계정의 권한 범위 안에서만 열려요.</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 매일 마이페이지 → 관리자 대시보드 순서로 우리 대리점 지표를 확인하세요.</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="n"/>
       <c r="C25" s="33" t="n"/>
       <c r="D25" s="33" t="n"/>
       <c r="E25" s="33" t="n"/>
       <c r="F25" s="33" t="n"/>
     </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>권한(대리점)에 따라 보이는 메뉴·데이터가 자동으로 정해져요.</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+    </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 마이페이지·관리자 대시보드 모두 로그인한 대리점 계정의 권한 범위 안에서만 열려요.</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="37" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매일 마이페이지 → 관리자 대시보드 순서로 우리 대리점 지표를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>03  🏠 대리점 대시보드  —  내 학생·매출·오늘 수업</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>📖 로그인하면 우리 대리점의 재원생·매출·오늘 수업이 카드로 정리돼 있어요. 검색창으로 원하는 기능을 바로 찾을 수 있어요.</t>
         </is>
       </c>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 오늘 매출·재원생·출석률   ›   2 카테고리 카드   ›   3 기능 검색창   ›   4 실시간 수업(LIVE)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="27" t="n">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>상단에서 오늘 매출·재원생·출석률(우리 대리점)을 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="27" t="n">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>카테고리 카드(학생·회계·콘텐츠 등)에서 기능을 눌러요.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="27" t="n">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>기능 검색창에 단어를 넣으면 바로 이동해요.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="27" t="n">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>실시간 수업(LIVE) 상태를 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="29" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>숫자는 ‘우리 대리점 범위’로 자동 집계돼요.</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>찾는 기능이 안 보이면 검색이 가장 빨라요.</t>
         </is>
       </c>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="F39" s="33" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 매일 아침 지표를 확인하면 우리 학원 상태를 빨리 파악할 수 있어요.</t>
         </is>
       </c>
-      <c r="B36" s="33" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="35" t="n"/>
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="35" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>04  🤖 AI 운영비서 활용  —  말·글로 조회·처리</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>📖 검색/마이크에 말하거나 글로 시키면 AI가 우리 대리점 범위에서 조회·처리를 도와줘요. 바쁜 상담 시간에 특히 편해요.</t>
         </is>
       </c>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
-      <c r="E39" s="24" t="n"/>
-      <c r="F39" s="24" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="B43" s="24" t="n"/>
+      <c r="C43" s="24" t="n"/>
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="24" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 검색/마이크   ›   2 조회   ›   3 ‘할까요?’로 먼저 확인</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="27" t="n">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>가운데 검색/마이크에 말하거나 입력해요. 예) “오늘 매출 어때?”</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="27" t="n">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>AI가 조회하거나 화면을 열어줘요. 예) “학생관리 열어줘”</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="27" t="n">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>중요한 처리는 ‘할까요?’로 먼저 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>말로 시키면 클릭보다 훨씬 빨라요.</t>
         </is>
       </c>
-      <c r="C44" s="31" t="n"/>
-      <c r="D44" s="31" t="n"/>
-      <c r="E44" s="31" t="n"/>
-      <c r="F44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="C49" s="33" t="n"/>
+      <c r="D49" s="33" t="n"/>
+      <c r="E49" s="33" t="n"/>
+      <c r="F49" s="33" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="B50" s="32" t="inlineStr">
         <is>
           <t>권한이 있는 일만 안전하게 처리해요.</t>
         </is>
       </c>
-      <c r="C45" s="31" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="31" t="n"/>
-      <c r="F45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="C50" s="33" t="n"/>
+      <c r="D50" s="33" t="n"/>
+      <c r="E50" s="33" t="n"/>
+      <c r="F50" s="33" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 버튼을 못 찾을 땐 ‘○○ 열어줘’라고 말해보세요.</t>
         </is>
       </c>
-      <c r="B46" s="33" t="n"/>
-      <c r="C46" s="33" t="n"/>
-      <c r="D46" s="33" t="n"/>
-      <c r="E46" s="33" t="n"/>
-      <c r="F46" s="33" t="n"/>
-    </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>05  🧑‍🎓 학생 모집·등록·관리  —  상담부터 등록까지</t>
-        </is>
-      </c>
-      <c r="B48" s="22" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="22" t="n"/>
-      <c r="F48" s="22" t="n"/>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="B51" s="35" t="n"/>
+      <c r="C51" s="35" t="n"/>
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="35" t="n"/>
+      <c r="F51" s="35" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1"/>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>05  🎓 학생 모집·등록·관리  —  상담부터 등록까지</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>📖 신규 상담을 접수하고 학생을 등록하며, 재원생의 출결·성적·이력을 관리해요. 우리 대리점의 핵심 업무예요.</t>
         </is>
       </c>
-      <c r="B49" s="24" t="n"/>
-      <c r="C49" s="24" t="n"/>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="24" t="n"/>
-      <c r="F49" s="24" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 신규 상담   ›   2 학생/학부모   ›   3 출결·평가·포인트·채팅…   ›   4 관리가 필요한 학생을 표…</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="n"/>
+      <c r="C56" s="26" t="n"/>
+      <c r="D56" s="26" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="26" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B57" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="27" t="n">
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B51" s="28" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>신규 상담을 접수하고 등록으로 전환해요.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="27" t="n">
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B52" s="28" t="inlineStr">
+      <c r="B59" s="30" t="inlineStr">
         <is>
           <t>학생/학부모에서 재원생 목록·이력을 관리해요.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="27" t="n">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="28" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>출결·평가·포인트·채팅 이력을 학생별로 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="27" t="n">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B54" s="28" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>관리가 필요한 학생을 표시해 챙겨요.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="29" t="inlineStr">
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B62" s="32" t="inlineStr">
         <is>
           <t>학생 목록은 실제 회원 데이터와 연동돼 있어요.</t>
         </is>
       </c>
-      <c r="C55" s="31" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="31" t="n"/>
-      <c r="F55" s="31" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="C62" s="33" t="n"/>
+      <c r="D62" s="33" t="n"/>
+      <c r="E62" s="33" t="n"/>
+      <c r="F62" s="33" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>상담→등록 전환율을 높이는 게 성장의 핵심이에요.</t>
         </is>
       </c>
-      <c r="C56" s="31" t="n"/>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="31" t="n"/>
-      <c r="F56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="C63" s="33" t="n"/>
+      <c r="D63" s="33" t="n"/>
+      <c r="E63" s="33" t="n"/>
+      <c r="F63" s="33" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 상담 기록을 꼼꼼히 남기면 재상담·등록 전환에 큰 도움이 돼요.</t>
         </is>
       </c>
-      <c r="B57" s="33" t="n"/>
-      <c r="C57" s="33" t="n"/>
-      <c r="D57" s="33" t="n"/>
-      <c r="E57" s="33" t="n"/>
-      <c r="F57" s="33" t="n"/>
-    </row>
-    <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="21" t="inlineStr">
-        <is>
-          <t>06  👨‍👩‍👧 학부모 소통  —  마이페이지 안내</t>
-        </is>
-      </c>
-      <c r="B59" s="22" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="22" t="n"/>
-      <c r="E59" s="22" t="n"/>
-      <c r="F59" s="22" t="n"/>
-    </row>
-    <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="B64" s="35" t="n"/>
+      <c r="C64" s="35" t="n"/>
+      <c r="D64" s="35" t="n"/>
+      <c r="E64" s="35" t="n"/>
+      <c r="F64" s="35" t="n"/>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="21" t="inlineStr">
+        <is>
+          <t>06  👪 학부모 소통  —  마이페이지 안내</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="23" t="inlineStr">
         <is>
           <t>📖 학부모가 자녀의 학습을 스스로 확인하도록 마이페이지를 안내해요. 상담 문의를 줄이고 만족도·재등록을 높여요.</t>
         </is>
       </c>
-      <c r="B60" s="24" t="n"/>
-      <c r="C60" s="24" t="n"/>
-      <c r="D60" s="24" t="n"/>
-      <c r="E60" s="24" t="n"/>
-      <c r="F60" s="24" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="25" t="inlineStr">
+      <c r="B67" s="24" t="n"/>
+      <c r="C67" s="24" t="n"/>
+      <c r="D67" s="24" t="n"/>
+      <c r="E67" s="24" t="n"/>
+      <c r="F67" s="24" t="n"/>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 마이페이지 링크   ›   2 자녀 학생 ID   ›   3 월별 보고서</t>
+        </is>
+      </c>
+      <c r="B68" s="26" t="n"/>
+      <c r="C68" s="26" t="n"/>
+      <c r="D68" s="26" t="n"/>
+      <c r="E68" s="26" t="n"/>
+      <c r="F68" s="26" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B61" s="26" t="inlineStr">
+      <c r="B69" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="27" t="n">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B62" s="28" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>학부모에게 마이페이지 링크를 안내해요.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="27" t="n">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="28" t="inlineStr">
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>학부모가 자녀 학생 ID로 출석·평가·결제·리포트를 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="27" t="n">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="28" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>월별 보고서(인쇄·PDF)로 성장 흐름을 공유해요.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>학부모 만족도가 재등록률로 이어져요.</t>
         </is>
       </c>
-      <c r="C65" s="31" t="n"/>
-      <c r="D65" s="31" t="n"/>
-      <c r="E65" s="31" t="n"/>
-      <c r="F65" s="31" t="n"/>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="29" t="inlineStr">
+      <c r="C73" s="33" t="n"/>
+      <c r="D73" s="33" t="n"/>
+      <c r="E73" s="33" t="n"/>
+      <c r="F73" s="33" t="n"/>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B74" s="32" t="inlineStr">
         <is>
           <t>학생 ID는 비밀번호처럼 관리하도록 안내하세요.</t>
         </is>
       </c>
-      <c r="C66" s="31" t="n"/>
-      <c r="D66" s="31" t="n"/>
-      <c r="E66" s="31" t="n"/>
-      <c r="F66" s="31" t="n"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="32" t="inlineStr">
+      <c r="C74" s="33" t="n"/>
+      <c r="D74" s="33" t="n"/>
+      <c r="E74" s="33" t="n"/>
+      <c r="F74" s="33" t="n"/>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 정기적으로 평가서를 함께 읽어주면 학부모 신뢰가 커져요.</t>
         </is>
       </c>
-      <c r="B67" s="33" t="n"/>
-      <c r="C67" s="33" t="n"/>
-      <c r="D67" s="33" t="n"/>
-      <c r="E67" s="33" t="n"/>
-      <c r="F67" s="33" t="n"/>
-    </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="B75" s="35" t="n"/>
+      <c r="C75" s="35" t="n"/>
+      <c r="D75" s="35" t="n"/>
+      <c r="E75" s="35" t="n"/>
+      <c r="F75" s="35" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1"/>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="21" t="inlineStr">
         <is>
           <t>07  📅 수업 예약·배정  —  일정과 강사 배정</t>
         </is>
       </c>
-      <c r="B69" s="22" t="n"/>
-      <c r="C69" s="22" t="n"/>
-      <c r="D69" s="22" t="n"/>
-      <c r="E69" s="22" t="n"/>
-      <c r="F69" s="22" t="n"/>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="23" t="inlineStr">
+      <c r="B78" s="22" t="n"/>
+      <c r="C78" s="22" t="n"/>
+      <c r="D78" s="22" t="n"/>
+      <c r="E78" s="22" t="n"/>
+      <c r="F78" s="22" t="n"/>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
         <is>
           <t>📖 학생의 수업 형태·시간·강사를 배정하고, 예약 현황을 관리해요. 연기·변경 요청도 처리해요.</t>
         </is>
       </c>
-      <c r="B70" s="24" t="n"/>
-      <c r="C70" s="24" t="n"/>
-      <c r="D70" s="24" t="n"/>
-      <c r="E70" s="24" t="n"/>
-      <c r="F70" s="24" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="25" t="inlineStr">
+      <c r="B79" s="24" t="n"/>
+      <c r="C79" s="24" t="n"/>
+      <c r="D79" s="24" t="n"/>
+      <c r="E79" s="24" t="n"/>
+      <c r="F79" s="24" t="n"/>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 예약   ›   2 빈 시간·중복을 확인해…   ›   3 연기/변경 요청</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="n"/>
+      <c r="C80" s="26" t="n"/>
+      <c r="D80" s="26" t="n"/>
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="26" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B81" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="27" t="n">
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B72" s="28" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>예약 화면에서 수업 형태·강사·시간을 배정해요.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="27" t="n">
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B73" s="28" t="inlineStr">
+      <c r="B83" s="30" t="inlineStr">
         <is>
           <t>빈 시간·중복을 확인해 조정해요.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="27" t="n">
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B74" s="28" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>학생의 연기/변경 요청을 규정에 맞게 처리해요.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>인기 시간대는 미리 배정해 두면 좋아요.</t>
         </is>
       </c>
-      <c r="C75" s="31" t="n"/>
-      <c r="D75" s="31" t="n"/>
-      <c r="E75" s="31" t="n"/>
-      <c r="F75" s="31" t="n"/>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="29" t="inlineStr">
+      <c r="C85" s="33" t="n"/>
+      <c r="D85" s="33" t="n"/>
+      <c r="E85" s="33" t="n"/>
+      <c r="F85" s="33" t="n"/>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B86" s="32" t="inlineStr">
         <is>
           <t>연기 마감 규정을 안내하면 노쇼가 줄어요.</t>
         </is>
       </c>
-      <c r="C76" s="31" t="n"/>
-      <c r="D76" s="31" t="n"/>
-      <c r="E76" s="31" t="n"/>
-      <c r="F76" s="31" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="32" t="inlineStr">
+      <c r="C86" s="33" t="n"/>
+      <c r="D86" s="33" t="n"/>
+      <c r="E86" s="33" t="n"/>
+      <c r="F86" s="33" t="n"/>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 강사별 가능 시간을 등록해두면 배정이 빨라져요.</t>
         </is>
       </c>
-      <c r="B77" s="33" t="n"/>
-      <c r="C77" s="33" t="n"/>
-      <c r="D77" s="33" t="n"/>
-      <c r="E77" s="33" t="n"/>
-      <c r="F77" s="33" t="n"/>
-    </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="21" t="inlineStr">
+      <c r="B87" s="35" t="n"/>
+      <c r="C87" s="35" t="n"/>
+      <c r="D87" s="35" t="n"/>
+      <c r="E87" s="35" t="n"/>
+      <c r="F87" s="35" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1"/>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
         <is>
           <t>08  💳 결제·수납 관리  —  결제·미납·환불</t>
         </is>
       </c>
-      <c r="B79" s="22" t="n"/>
-      <c r="C79" s="22" t="n"/>
-      <c r="D79" s="22" t="n"/>
-      <c r="E79" s="22" t="n"/>
-      <c r="F79" s="22" t="n"/>
-    </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="23" t="inlineStr">
+      <c r="B90" s="22" t="n"/>
+      <c r="C90" s="22" t="n"/>
+      <c r="D90" s="22" t="n"/>
+      <c r="E90" s="22" t="n"/>
+      <c r="F90" s="22" t="n"/>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="23" t="inlineStr">
         <is>
           <t>📖 우리 대리점의 결제·미납·환불을 처리해요. 규정에 따라 금액이 자동 계산되고, 미납은 알림으로 관리해요.</t>
         </is>
       </c>
-      <c r="B80" s="24" t="n"/>
-      <c r="C80" s="24" t="n"/>
-      <c r="D80" s="24" t="n"/>
-      <c r="E80" s="24" t="n"/>
-      <c r="F80" s="24" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="25" t="inlineStr">
+      <c r="B91" s="24" t="n"/>
+      <c r="C91" s="24" t="n"/>
+      <c r="D91" s="24" t="n"/>
+      <c r="E91" s="24" t="n"/>
+      <c r="F91" s="24" t="n"/>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 회계/포인트   ›   2 알림톡·문자   ›   3 환불 규정표</t>
+        </is>
+      </c>
+      <c r="B92" s="26" t="n"/>
+      <c r="C92" s="26" t="n"/>
+      <c r="D92" s="26" t="n"/>
+      <c r="E92" s="26" t="n"/>
+      <c r="F92" s="26" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B81" s="26" t="inlineStr">
+      <c r="B93" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="27" t="n">
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B82" s="28" t="inlineStr">
+      <c r="B94" s="30" t="inlineStr">
         <is>
           <t>회계/포인트에서 결제·미납·환불을 처리해요.</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="27" t="n">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="28" t="inlineStr">
+      <c r="B95" s="30" t="inlineStr">
         <is>
           <t>미납 건은 알림톡·문자로 안내해요.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="27" t="n">
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="B96" s="30" t="inlineStr">
         <is>
           <t>환불 규정표에 따라 금액이 자동 계산돼요.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="29" t="inlineStr">
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B85" s="30" t="inlineStr">
+      <c r="B97" s="32" t="inlineStr">
         <is>
           <t>미납 알림 자동화로 수납률을 높이세요.</t>
         </is>
       </c>
-      <c r="C85" s="31" t="n"/>
-      <c r="D85" s="31" t="n"/>
-      <c r="E85" s="31" t="n"/>
-      <c r="F85" s="31" t="n"/>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B86" s="30" t="inlineStr">
-        <is>
-          <t>할인 결제 환불은 정가 기준으로 재정산돼요.</t>
-        </is>
-      </c>
-      <c r="C86" s="31" t="n"/>
-      <c r="D86" s="31" t="n"/>
-      <c r="E86" s="31" t="n"/>
-      <c r="F86" s="31" t="n"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 수납 현황을 주기적으로 점검하면 매출이 안정돼요.</t>
-        </is>
-      </c>
-      <c r="B87" s="33" t="n"/>
-      <c r="C87" s="33" t="n"/>
-      <c r="D87" s="33" t="n"/>
-      <c r="E87" s="33" t="n"/>
-      <c r="F87" s="33" t="n"/>
-    </row>
-    <row r="89" ht="26" customHeight="1">
-      <c r="A89" s="21" t="inlineStr">
-        <is>
-          <t>09  📈 학생 학습 현황·리포트  —  진도·성과 확인</t>
-        </is>
-      </c>
-      <c r="B89" s="22" t="n"/>
-      <c r="C89" s="22" t="n"/>
-      <c r="D89" s="22" t="n"/>
-      <c r="E89" s="22" t="n"/>
-      <c r="F89" s="22" t="n"/>
-    </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="23" t="inlineStr">
-        <is>
-          <t>📖 우리 학생들의 출석·평가·학습 진도를 확인하고, 리포트로 성과를 점검해요. 학부모 상담·재등록 설득에 활용해요.</t>
-        </is>
-      </c>
-      <c r="B90" s="24" t="n"/>
-      <c r="C90" s="24" t="n"/>
-      <c r="D90" s="24" t="n"/>
-      <c r="E90" s="24" t="n"/>
-      <c r="F90" s="24" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B91" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B92" s="28" t="inlineStr">
-        <is>
-          <t>학생별 출석·평가·학습 진도를 확인해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B93" s="28" t="inlineStr">
-        <is>
-          <t>월별 보고서로 성과를 정리해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B94" s="28" t="inlineStr">
-        <is>
-          <t>리포트를 학부모 상담에 활용해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B95" s="30" t="inlineStr">
-        <is>
-          <t>데이터로 보여주면 학부모 신뢰가 커져요.</t>
-        </is>
-      </c>
-      <c r="C95" s="31" t="n"/>
-      <c r="D95" s="31" t="n"/>
-      <c r="E95" s="31" t="n"/>
-      <c r="F95" s="31" t="n"/>
-    </row>
-    <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B96" s="30" t="inlineStr">
-        <is>
-          <t>성과가 좋은 학생은 후기·추천으로 연결하세요.</t>
-        </is>
-      </c>
-      <c r="C96" s="31" t="n"/>
-      <c r="D96" s="31" t="n"/>
-      <c r="E96" s="31" t="n"/>
-      <c r="F96" s="31" t="n"/>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 재등록 시점 전에 리포트로 성과를 보여주면 설득이 쉬워요.</t>
-        </is>
-      </c>
-      <c r="B97" s="33" t="n"/>
       <c r="C97" s="33" t="n"/>
       <c r="D97" s="33" t="n"/>
       <c r="E97" s="33" t="n"/>
       <c r="F97" s="33" t="n"/>
     </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="A99" s="21" t="inlineStr">
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B98" s="32" t="inlineStr">
+        <is>
+          <t>할인 결제 환불은 정가 기준으로 재정산돼요.</t>
+        </is>
+      </c>
+      <c r="C98" s="33" t="n"/>
+      <c r="D98" s="33" t="n"/>
+      <c r="E98" s="33" t="n"/>
+      <c r="F98" s="33" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 수납 현황을 주기적으로 점검하면 매출이 안정돼요.</t>
+        </is>
+      </c>
+      <c r="B99" s="35" t="n"/>
+      <c r="C99" s="35" t="n"/>
+      <c r="D99" s="35" t="n"/>
+      <c r="E99" s="35" t="n"/>
+      <c r="F99" s="35" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1"/>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>09  📈 학생 학습 현황·리포트  —  진도·성과 확인</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="n"/>
+      <c r="C102" s="22" t="n"/>
+      <c r="D102" s="22" t="n"/>
+      <c r="E102" s="22" t="n"/>
+      <c r="F102" s="22" t="n"/>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="23" t="inlineStr">
+        <is>
+          <t>📖 우리 학생들의 출석·평가·학습 진도를 확인하고, 리포트로 성과를 점검해요. 학부모 상담·재등록 설득에 활용해요.</t>
+        </is>
+      </c>
+      <c r="B103" s="24" t="n"/>
+      <c r="C103" s="24" t="n"/>
+      <c r="D103" s="24" t="n"/>
+      <c r="E103" s="24" t="n"/>
+      <c r="F103" s="24" t="n"/>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 출석·평가·학습 진도   ›   2 월별 보고서   ›   3 학부모 상담</t>
+        </is>
+      </c>
+      <c r="B104" s="26" t="n"/>
+      <c r="C104" s="26" t="n"/>
+      <c r="D104" s="26" t="n"/>
+      <c r="E104" s="26" t="n"/>
+      <c r="F104" s="26" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B105" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B106" s="30" t="inlineStr">
+        <is>
+          <t>학생별 출석·평가·학습 진도를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B107" s="30" t="inlineStr">
+        <is>
+          <t>월별 보고서로 성과를 정리해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B108" s="30" t="inlineStr">
+        <is>
+          <t>리포트를 학부모 상담에 활용해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>데이터로 보여주면 학부모 신뢰가 커져요.</t>
+        </is>
+      </c>
+      <c r="C109" s="33" t="n"/>
+      <c r="D109" s="33" t="n"/>
+      <c r="E109" s="33" t="n"/>
+      <c r="F109" s="33" t="n"/>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>성과가 좋은 학생은 후기·추천으로 연결하세요.</t>
+        </is>
+      </c>
+      <c r="C110" s="33" t="n"/>
+      <c r="D110" s="33" t="n"/>
+      <c r="E110" s="33" t="n"/>
+      <c r="F110" s="33" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 재등록 시점 전에 리포트로 성과를 보여주면 설득이 쉬워요.</t>
+        </is>
+      </c>
+      <c r="B111" s="35" t="n"/>
+      <c r="C111" s="35" t="n"/>
+      <c r="D111" s="35" t="n"/>
+      <c r="E111" s="35" t="n"/>
+      <c r="F111" s="35" t="n"/>
+    </row>
+    <row r="112" ht="18" customHeight="1"/>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="21" t="inlineStr">
         <is>
           <t>10  🌳 대리점 정산  —  지사→대리점 수령</t>
         </is>
       </c>
-      <c r="B99" s="22" t="n"/>
-      <c r="C99" s="22" t="n"/>
-      <c r="D99" s="22" t="n"/>
-      <c r="E99" s="22" t="n"/>
-      <c r="F99" s="22" t="n"/>
-    </row>
-    <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="23" t="inlineStr">
+      <c r="B114" s="22" t="n"/>
+      <c r="C114" s="22" t="n"/>
+      <c r="D114" s="22" t="n"/>
+      <c r="E114" s="22" t="n"/>
+      <c r="F114" s="22" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="23" t="inlineStr">
         <is>
           <t>📖 지사에서 우리 대리점으로 내려오는 정산을 확인해요. 매출·수수료가 조직 트리 구조로 자동 계산돼, 내 몫을 투명하게 알 수 있어요.</t>
         </is>
       </c>
-      <c r="B100" s="24" t="n"/>
-      <c r="C100" s="24" t="n"/>
-      <c r="D100" s="24" t="n"/>
-      <c r="E100" s="24" t="n"/>
-      <c r="F100" s="24" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="25" t="inlineStr">
+      <c r="B115" s="24" t="n"/>
+      <c r="C115" s="24" t="n"/>
+      <c r="D115" s="24" t="n"/>
+      <c r="E115" s="24" t="n"/>
+      <c r="F115" s="24" t="n"/>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="A116" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 지사→대리점 정산   ›   2 매출·수수료 계산 내역을…   ›   3 저장(PDF)</t>
+        </is>
+      </c>
+      <c r="B116" s="26" t="n"/>
+      <c r="C116" s="26" t="n"/>
+      <c r="D116" s="26" t="n"/>
+      <c r="E116" s="26" t="n"/>
+      <c r="F116" s="26" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B101" s="26" t="inlineStr">
+      <c r="B117" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="27" t="n">
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B102" s="28" t="inlineStr">
+      <c r="B118" s="30" t="inlineStr">
         <is>
           <t>지사→대리점 정산(수령액)을 월별로 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="27" t="n">
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B103" s="28" t="inlineStr">
+      <c r="B119" s="30" t="inlineStr">
         <is>
           <t>매출·수수료 계산 내역을 점검해요.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="27" t="n">
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B104" s="28" t="inlineStr">
+      <c r="B120" s="30" t="inlineStr">
         <is>
           <t>정산 리포트를 저장(PDF) 해 보관해요.</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="24" customHeight="1">
-      <c r="A105" s="29" t="inlineStr">
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B105" s="30" t="inlineStr">
+      <c r="B121" s="32" t="inlineStr">
         <is>
           <t>정산은 조직 트리 구조로 자동 계산돼요.</t>
         </is>
       </c>
-      <c r="C105" s="31" t="n"/>
-      <c r="D105" s="31" t="n"/>
-      <c r="E105" s="31" t="n"/>
-      <c r="F105" s="31" t="n"/>
-    </row>
-    <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="29" t="inlineStr">
+      <c r="C121" s="33" t="n"/>
+      <c r="D121" s="33" t="n"/>
+      <c r="E121" s="33" t="n"/>
+      <c r="F121" s="33" t="n"/>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B106" s="30" t="inlineStr">
+      <c r="B122" s="32" t="inlineStr">
         <is>
           <t>이상 항목은 지사·본사에 문의해 확인하세요.</t>
         </is>
       </c>
-      <c r="C106" s="31" t="n"/>
-      <c r="D106" s="31" t="n"/>
-      <c r="E106" s="31" t="n"/>
-      <c r="F106" s="31" t="n"/>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="32" t="inlineStr">
+      <c r="C122" s="33" t="n"/>
+      <c r="D122" s="33" t="n"/>
+      <c r="E122" s="33" t="n"/>
+      <c r="F122" s="33" t="n"/>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 매출과 정산을 함께 보면 우리 대리점 수익 구조가 명확해져요.</t>
         </is>
       </c>
-      <c r="B107" s="33" t="n"/>
-      <c r="C107" s="33" t="n"/>
-      <c r="D107" s="33" t="n"/>
-      <c r="E107" s="33" t="n"/>
-      <c r="F107" s="33" t="n"/>
-    </row>
-    <row r="109" ht="26" customHeight="1">
-      <c r="A109" s="21" t="inlineStr">
+      <c r="B123" s="35" t="n"/>
+      <c r="C123" s="35" t="n"/>
+      <c r="D123" s="35" t="n"/>
+      <c r="E123" s="35" t="n"/>
+      <c r="F123" s="35" t="n"/>
+    </row>
+    <row r="124" ht="18" customHeight="1"/>
+    <row r="126" ht="26" customHeight="1">
+      <c r="A126" s="21" t="inlineStr">
         <is>
           <t>11  🧲 이탈 방지 (내 학생 케어)  —  이탈위험 조기 발견</t>
         </is>
       </c>
-      <c r="B109" s="22" t="n"/>
-      <c r="C109" s="22" t="n"/>
-      <c r="D109" s="22" t="n"/>
-      <c r="E109" s="22" t="n"/>
-      <c r="F109" s="22" t="n"/>
-    </row>
-    <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="23" t="inlineStr">
+      <c r="B126" s="22" t="n"/>
+      <c r="C126" s="22" t="n"/>
+      <c r="D126" s="22" t="n"/>
+      <c r="E126" s="22" t="n"/>
+      <c r="F126" s="22" t="n"/>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="23" t="inlineStr">
         <is>
           <t>📖 그만둘 것 같은 학생을 미리 찾아 케어해요. 결석이 잦거나 성과가 떨어지는 학생을 빠르게 챙기면 재등록률이 올라가요.</t>
         </is>
       </c>
-      <c r="B110" s="24" t="n"/>
-      <c r="C110" s="24" t="n"/>
-      <c r="D110" s="24" t="n"/>
-      <c r="E110" s="24" t="n"/>
-      <c r="F110" s="24" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="25" t="inlineStr">
+      <c r="B127" s="24" t="n"/>
+      <c r="C127" s="24" t="n"/>
+      <c r="D127" s="24" t="n"/>
+      <c r="E127" s="24" t="n"/>
+      <c r="F127" s="24" t="n"/>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 이탈위험   ›   2 상담·알림톡   ›   3 가족·추천 관계도 함께…</t>
+        </is>
+      </c>
+      <c r="B128" s="26" t="n"/>
+      <c r="C128" s="26" t="n"/>
+      <c r="D128" s="26" t="n"/>
+      <c r="E128" s="26" t="n"/>
+      <c r="F128" s="26" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B111" s="26" t="inlineStr">
+      <c r="B129" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="30" customHeight="1">
-      <c r="A112" s="27" t="n">
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B112" s="28" t="inlineStr">
+      <c r="B130" s="30" t="inlineStr">
         <is>
           <t>이탈위험 신호(결석·성과 하락)를 확인해요.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="30" customHeight="1">
-      <c r="A113" s="27" t="n">
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="28" t="inlineStr">
+      <c r="B131" s="30" t="inlineStr">
         <is>
           <t>위험 학생에 상담·알림톡으로 개입해요.</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="27" t="n">
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="28" t="inlineStr">
+      <c r="B132" s="30" t="inlineStr">
         <is>
           <t>가족·추천 관계도 함께 관리해요.</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="24" customHeight="1">
-      <c r="A115" s="29" t="inlineStr">
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B115" s="30" t="inlineStr">
+      <c r="B133" s="32" t="inlineStr">
         <is>
           <t>빨리 개입할수록 잔존율이 올라가요.</t>
         </is>
       </c>
-      <c r="C115" s="31" t="n"/>
-      <c r="D115" s="31" t="n"/>
-      <c r="E115" s="31" t="n"/>
-      <c r="F115" s="31" t="n"/>
-    </row>
-    <row r="116" ht="24" customHeight="1">
-      <c r="A116" s="29" t="inlineStr">
+      <c r="C133" s="33" t="n"/>
+      <c r="D133" s="33" t="n"/>
+      <c r="E133" s="33" t="n"/>
+      <c r="F133" s="33" t="n"/>
+    </row>
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B116" s="30" t="inlineStr">
+      <c r="B134" s="32" t="inlineStr">
         <is>
           <t>재등록 시즌 전 케어가 특히 중요해요.</t>
         </is>
       </c>
-      <c r="C116" s="31" t="n"/>
-      <c r="D116" s="31" t="n"/>
-      <c r="E116" s="31" t="n"/>
-      <c r="F116" s="31" t="n"/>
-    </row>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="32" t="inlineStr">
+      <c r="C134" s="33" t="n"/>
+      <c r="D134" s="33" t="n"/>
+      <c r="E134" s="33" t="n"/>
+      <c r="F134" s="33" t="n"/>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 매주 결석 잦은 학생부터 챙기면 이탈이 눈에 띄게 줄어요.</t>
         </is>
       </c>
-      <c r="B117" s="33" t="n"/>
-      <c r="C117" s="33" t="n"/>
-      <c r="D117" s="33" t="n"/>
-      <c r="E117" s="33" t="n"/>
-      <c r="F117" s="33" t="n"/>
-    </row>
-    <row r="119" ht="26" customHeight="1">
-      <c r="A119" s="21" t="inlineStr">
+      <c r="B135" s="35" t="n"/>
+      <c r="C135" s="35" t="n"/>
+      <c r="D135" s="35" t="n"/>
+      <c r="E135" s="35" t="n"/>
+      <c r="F135" s="35" t="n"/>
+    </row>
+    <row r="136" ht="18" customHeight="1"/>
+    <row r="138" ht="26" customHeight="1">
+      <c r="A138" s="21" t="inlineStr">
         <is>
           <t>12  💬 신규 상담·모객  —  문의 접수·전환</t>
         </is>
       </c>
-      <c r="B119" s="22" t="n"/>
-      <c r="C119" s="22" t="n"/>
-      <c r="D119" s="22" t="n"/>
-      <c r="E119" s="22" t="n"/>
-      <c r="F119" s="22" t="n"/>
-    </row>
-    <row r="120" ht="42" customHeight="1">
-      <c r="A120" s="23" t="inlineStr">
+      <c r="B138" s="22" t="n"/>
+      <c r="C138" s="22" t="n"/>
+      <c r="D138" s="22" t="n"/>
+      <c r="E138" s="22" t="n"/>
+      <c r="F138" s="22" t="n"/>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="23" t="inlineStr">
         <is>
           <t>📖 신규 상담·문의를 접수하고 등록으로 전환해요. 모객이 대리점 성장의 출발점이에요.</t>
         </is>
       </c>
-      <c r="B120" s="24" t="n"/>
-      <c r="C120" s="24" t="n"/>
-      <c r="D120" s="24" t="n"/>
-      <c r="E120" s="24" t="n"/>
-      <c r="F120" s="24" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="25" t="inlineStr">
+      <c r="B139" s="24" t="n"/>
+      <c r="C139" s="24" t="n"/>
+      <c r="D139" s="24" t="n"/>
+      <c r="E139" s="24" t="n"/>
+      <c r="F139" s="24" t="n"/>
+    </row>
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 신규 상담/문의   ›   2 등록으로 전환   ›   3 체험 수업·레벨테스트로…</t>
+        </is>
+      </c>
+      <c r="B140" s="26" t="n"/>
+      <c r="C140" s="26" t="n"/>
+      <c r="D140" s="26" t="n"/>
+      <c r="E140" s="26" t="n"/>
+      <c r="F140" s="26" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B121" s="26" t="inlineStr">
+      <c r="B141" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="27" t="n">
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B122" s="28" t="inlineStr">
+      <c r="B142" s="30" t="inlineStr">
         <is>
           <t>신규 상담/문의를 접수해요.</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="30" customHeight="1">
-      <c r="A123" s="27" t="n">
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B123" s="28" t="inlineStr">
+      <c r="B143" s="30" t="inlineStr">
         <is>
           <t>상담 내용을 기록하고 등록으로 전환해요.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="27" t="n">
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B124" s="28" t="inlineStr">
+      <c r="B144" s="30" t="inlineStr">
         <is>
           <t>체험 수업·레벨테스트로 등록을 유도해요.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="29" t="inlineStr">
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B125" s="30" t="inlineStr">
+      <c r="B145" s="32" t="inlineStr">
         <is>
           <t>빠른 응대가 등록 전환율을 높여요.</t>
         </is>
       </c>
-      <c r="C125" s="31" t="n"/>
-      <c r="D125" s="31" t="n"/>
-      <c r="E125" s="31" t="n"/>
-      <c r="F125" s="31" t="n"/>
-    </row>
-    <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="29" t="inlineStr">
+      <c r="C145" s="33" t="n"/>
+      <c r="D145" s="33" t="n"/>
+      <c r="E145" s="33" t="n"/>
+      <c r="F145" s="33" t="n"/>
+    </row>
+    <row r="146" ht="24" customHeight="1">
+      <c r="A146" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B126" s="30" t="inlineStr">
+      <c r="B146" s="32" t="inlineStr">
         <is>
           <t>체험→등록 흐름을 매끄럽게 만드세요.</t>
         </is>
       </c>
-      <c r="C126" s="31" t="n"/>
-      <c r="D126" s="31" t="n"/>
-      <c r="E126" s="31" t="n"/>
-      <c r="F126" s="31" t="n"/>
-    </row>
-    <row r="127" ht="30" customHeight="1">
-      <c r="A127" s="32" t="inlineStr">
+      <c r="C146" s="33" t="n"/>
+      <c r="D146" s="33" t="n"/>
+      <c r="E146" s="33" t="n"/>
+      <c r="F146" s="33" t="n"/>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 상담 후 후속 연락(팔로업)을 챙기면 전환율이 올라가요.</t>
         </is>
       </c>
-      <c r="B127" s="33" t="n"/>
-      <c r="C127" s="33" t="n"/>
-      <c r="D127" s="33" t="n"/>
-      <c r="E127" s="33" t="n"/>
-      <c r="F127" s="33" t="n"/>
-    </row>
-    <row r="129" ht="26" customHeight="1">
-      <c r="A129" s="21" t="inlineStr">
+      <c r="B147" s="35" t="n"/>
+      <c r="C147" s="35" t="n"/>
+      <c r="D147" s="35" t="n"/>
+      <c r="E147" s="35" t="n"/>
+      <c r="F147" s="35" t="n"/>
+    </row>
+    <row r="148" ht="18" customHeight="1"/>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="21" t="inlineStr">
         <is>
           <t>13  🎧 고객센터·지원  —  지사·본사 지원 받기</t>
         </is>
       </c>
-      <c r="B129" s="22" t="n"/>
-      <c r="C129" s="22" t="n"/>
-      <c r="D129" s="22" t="n"/>
-      <c r="E129" s="22" t="n"/>
-      <c r="F129" s="22" t="n"/>
-    </row>
-    <row r="130" ht="42" customHeight="1">
-      <c r="A130" s="23" t="inlineStr">
+      <c r="B150" s="22" t="n"/>
+      <c r="C150" s="22" t="n"/>
+      <c r="D150" s="22" t="n"/>
+      <c r="E150" s="22" t="n"/>
+      <c r="F150" s="22" t="n"/>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="23" t="inlineStr">
         <is>
           <t>📖 운영 중 문제가 생기면 지사·본사 고객센터로 문의해요. 시스템·정산·정책 문의를 빠르게 해결할 수 있어요.</t>
         </is>
       </c>
-      <c r="B130" s="24" t="n"/>
-      <c r="C130" s="24" t="n"/>
-      <c r="D130" s="24" t="n"/>
-      <c r="E130" s="24" t="n"/>
-      <c r="F130" s="24" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="25" t="inlineStr">
+      <c r="B151" s="24" t="n"/>
+      <c r="C151" s="24" t="n"/>
+      <c r="D151" s="24" t="n"/>
+      <c r="E151" s="24" t="n"/>
+      <c r="F151" s="24" t="n"/>
+    </row>
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 고객센터   ›   2 지사/본사   ›   3 대응 방법을 메모</t>
+        </is>
+      </c>
+      <c r="B152" s="26" t="n"/>
+      <c r="C152" s="26" t="n"/>
+      <c r="D152" s="26" t="n"/>
+      <c r="E152" s="26" t="n"/>
+      <c r="F152" s="26" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B131" s="26" t="inlineStr">
+      <c r="B153" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="30" customHeight="1">
-      <c r="A132" s="27" t="n">
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B132" s="28" t="inlineStr">
+      <c r="B154" s="30" t="inlineStr">
         <is>
           <t>고객센터에서 전화·이메일·카카오·원격지원을 이용해요.</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="30" customHeight="1">
-      <c r="A133" s="27" t="n">
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B133" s="28" t="inlineStr">
+      <c r="B155" s="30" t="inlineStr">
         <is>
           <t>정산·정책 문의는 지사/본사와 연결해요.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="30" customHeight="1">
-      <c r="A134" s="27" t="n">
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B134" s="28" t="inlineStr">
+      <c r="B156" s="30" t="inlineStr">
         <is>
           <t>반복 문제는 대응 방법을 메모해 둬요.</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="29" t="inlineStr">
+    <row r="157" ht="24" customHeight="1">
+      <c r="A157" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B135" s="30" t="inlineStr">
+      <c r="B157" s="32" t="inlineStr">
         <is>
           <t>시스템 문제는 원격지원으로 빠르게 해결돼요.</t>
         </is>
       </c>
-      <c r="C135" s="31" t="n"/>
-      <c r="D135" s="31" t="n"/>
-      <c r="E135" s="31" t="n"/>
-      <c r="F135" s="31" t="n"/>
-    </row>
-    <row r="136" ht="24" customHeight="1">
-      <c r="A136" s="29" t="inlineStr">
+      <c r="C157" s="33" t="n"/>
+      <c r="D157" s="33" t="n"/>
+      <c r="E157" s="33" t="n"/>
+      <c r="F157" s="33" t="n"/>
+    </row>
+    <row r="158" ht="24" customHeight="1">
+      <c r="A158" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B136" s="30" t="inlineStr">
+      <c r="B158" s="32" t="inlineStr">
         <is>
           <t>‘입장 안 됨’ 문의는 브라우저·권한부터 확인하세요.</t>
         </is>
       </c>
-      <c r="C136" s="31" t="n"/>
-      <c r="D136" s="31" t="n"/>
-      <c r="E136" s="31" t="n"/>
-      <c r="F136" s="31" t="n"/>
-    </row>
-    <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="32" t="inlineStr">
+      <c r="C158" s="33" t="n"/>
+      <c r="D158" s="33" t="n"/>
+      <c r="E158" s="33" t="n"/>
+      <c r="F158" s="33" t="n"/>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 자주 겪는 문의와 해결법을 정리해두면 상담이 빨라져요.</t>
         </is>
       </c>
-      <c r="B137" s="33" t="n"/>
-      <c r="C137" s="33" t="n"/>
-      <c r="D137" s="33" t="n"/>
-      <c r="E137" s="33" t="n"/>
-      <c r="F137" s="33" t="n"/>
-    </row>
-    <row r="139" ht="26" customHeight="1">
-      <c r="A139" s="21" t="inlineStr">
+      <c r="B159" s="35" t="n"/>
+      <c r="C159" s="35" t="n"/>
+      <c r="D159" s="35" t="n"/>
+      <c r="E159" s="35" t="n"/>
+      <c r="F159" s="35" t="n"/>
+    </row>
+    <row r="160" ht="18" customHeight="1"/>
+    <row r="162" ht="26" customHeight="1">
+      <c r="A162" s="21" t="inlineStr">
         <is>
           <t>14  🕐 한국·필리핀 듀얼 시계  —  화면에 뜨는 두 나라 시간</t>
         </is>
       </c>
-      <c r="B139" s="22" t="n"/>
-      <c r="C139" s="22" t="n"/>
-      <c r="D139" s="22" t="n"/>
-      <c r="E139" s="22" t="n"/>
-      <c r="F139" s="22" t="n"/>
-    </row>
-    <row r="140" ht="42" customHeight="1">
-      <c r="A140" s="23" t="inlineStr">
+      <c r="B162" s="22" t="n"/>
+      <c r="C162" s="22" t="n"/>
+      <c r="D162" s="22" t="n"/>
+      <c r="E162" s="22" t="n"/>
+      <c r="F162" s="22" t="n"/>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="23" t="inlineStr">
         <is>
           <t>📖 화면에 🇰🇷 한국·🇵🇭 필리핀 시간이 함께 뜨는 시계예요. 필리핀 현지 강사와 한국 학생의 수업 시간을 조율할 때 시차를 바로 확인할 수 있어요.</t>
         </is>
       </c>
-      <c r="B140" s="24" t="n"/>
-      <c r="C140" s="24" t="n"/>
-      <c r="D140" s="24" t="n"/>
-      <c r="E140" s="24" t="n"/>
-      <c r="F140" s="24" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="25" t="inlineStr">
+      <c r="B163" s="24" t="n"/>
+      <c r="C163" s="24" t="n"/>
+      <c r="D163" s="24" t="n"/>
+      <c r="E163" s="24" t="n"/>
+      <c r="F163" s="24" t="n"/>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 듀얼 시계   ›   2 드래그   ›   3 탭(클릭)</t>
+        </is>
+      </c>
+      <c r="B164" s="26" t="n"/>
+      <c r="C164" s="26" t="n"/>
+      <c r="D164" s="26" t="n"/>
+      <c r="E164" s="26" t="n"/>
+      <c r="F164" s="26" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B141" s="26" t="inlineStr">
+      <c r="B165" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="30" customHeight="1">
-      <c r="A142" s="27" t="n">
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B142" s="28" t="inlineStr">
+      <c r="B166" s="30" t="inlineStr">
         <is>
           <t>화면에 떠 있는 듀얼 시계에서 🇰🇷 한국·🇵🇭 필리핀 시간을 동시에 봐요.</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="30" customHeight="1">
-      <c r="A143" s="27" t="n">
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B143" s="28" t="inlineStr">
+      <c r="B167" s="30" t="inlineStr">
         <is>
           <t>시계를 드래그하면 원하는 위치로 옮길 수 있어요.</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="30" customHeight="1">
-      <c r="A144" s="27" t="n">
+    <row r="168" ht="30" customHeight="1">
+      <c r="A168" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B144" s="28" t="inlineStr">
+      <c r="B168" s="30" t="inlineStr">
         <is>
           <t>시계를 탭(클릭)하면 홈으로 이동해요.</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="24" customHeight="1">
-      <c r="A145" s="29" t="inlineStr">
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B145" s="30" t="inlineStr">
+      <c r="B169" s="32" t="inlineStr">
         <is>
           <t>필리핀은 한국보다 1시간 느려요(시차 −1시간).</t>
         </is>
       </c>
-      <c r="C145" s="31" t="n"/>
-      <c r="D145" s="31" t="n"/>
-      <c r="E145" s="31" t="n"/>
-      <c r="F145" s="31" t="n"/>
-    </row>
-    <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="29" t="inlineStr">
+      <c r="C169" s="33" t="n"/>
+      <c r="D169" s="33" t="n"/>
+      <c r="E169" s="33" t="n"/>
+      <c r="F169" s="33" t="n"/>
+    </row>
+    <row r="170" ht="24" customHeight="1">
+      <c r="A170" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B146" s="30" t="inlineStr">
+      <c r="B170" s="32" t="inlineStr">
         <is>
           <t>수업 예약·입장 시간을 두 나라 시간으로 확인할 수 있어요.</t>
         </is>
       </c>
-      <c r="C146" s="31" t="n"/>
-      <c r="D146" s="31" t="n"/>
-      <c r="E146" s="31" t="n"/>
-      <c r="F146" s="31" t="n"/>
-    </row>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="32" t="inlineStr">
+      <c r="C170" s="33" t="n"/>
+      <c r="D170" s="33" t="n"/>
+      <c r="E170" s="33" t="n"/>
+      <c r="F170" s="33" t="n"/>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 시차 때문에 수업 시간이 헷갈릴 때 이 시계를 보면 바로 확인돼요.</t>
         </is>
       </c>
-      <c r="B147" s="33" t="n"/>
-      <c r="C147" s="33" t="n"/>
-      <c r="D147" s="33" t="n"/>
-      <c r="E147" s="33" t="n"/>
-      <c r="F147" s="33" t="n"/>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="21" t="inlineStr">
+      <c r="B171" s="35" t="n"/>
+      <c r="C171" s="35" t="n"/>
+      <c r="D171" s="35" t="n"/>
+      <c r="E171" s="35" t="n"/>
+      <c r="F171" s="35" t="n"/>
+    </row>
+    <row r="172" ht="18" customHeight="1"/>
+    <row r="174" ht="26" customHeight="1">
+      <c r="A174" s="21" t="inlineStr">
         <is>
           <t>15  🇨🇳 중국어 발음 코치  —  다락원 중국어 마스터 Lv1~20</t>
         </is>
       </c>
-      <c r="B149" s="22" t="n"/>
-      <c r="C149" s="22" t="n"/>
-      <c r="D149" s="22" t="n"/>
-      <c r="E149" s="22" t="n"/>
-      <c r="F149" s="22" t="n"/>
-    </row>
-    <row r="150" ht="42" customHeight="1">
-      <c r="A150" s="23" t="inlineStr">
+      <c r="B174" s="22" t="n"/>
+      <c r="C174" s="22" t="n"/>
+      <c r="D174" s="22" t="n"/>
+      <c r="E174" s="22" t="n"/>
+      <c r="F174" s="22" t="n"/>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="23" t="inlineStr">
         <is>
           <t>📖 망고아이는 영어뿐 아니라 중국어 과정도 제공해요. 다락원 중국어 마스터(Lv 1~20) 기반 발음 코치(한자+병음·AI 음성인식·원어민 비교)로, 중국어 수요가 있는 학생을 유치·관리할 수 있어요.</t>
         </is>
       </c>
-      <c r="B150" s="24" t="n"/>
-      <c r="C150" s="24" t="n"/>
-      <c r="D150" s="24" t="n"/>
-      <c r="E150" s="24" t="n"/>
-      <c r="F150" s="24" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="25" t="inlineStr">
+      <c r="B175" s="24" t="n"/>
+      <c r="C175" s="24" t="n"/>
+      <c r="D175" s="24" t="n"/>
+      <c r="E175" s="24" t="n"/>
+      <c r="F175" s="24" t="n"/>
+    </row>
+    <row r="176" ht="24" customHeight="1">
+      <c r="A176" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 CN 중국어   ›   2 다락원 마스터 시리즈(1…   ›   3 한자 + 병음   ›   4 반복·느리게(0.85x)</t>
+        </is>
+      </c>
+      <c r="B176" s="26" t="n"/>
+      <c r="C176" s="26" t="n"/>
+      <c r="D176" s="26" t="n"/>
+      <c r="E176" s="26" t="n"/>
+      <c r="F176" s="26" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B151" s="26" t="inlineStr">
+      <c r="B177" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="30" customHeight="1">
-      <c r="A152" s="27" t="n">
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B152" s="28" t="inlineStr">
+      <c r="B178" s="30" t="inlineStr">
         <is>
           <t>AI 음성코치에서 CN 중국어 레벨을 골라요. (또는 중국어 발음 코치로 이동)</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="30" customHeight="1">
-      <c r="A153" s="27" t="n">
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B153" s="28" t="inlineStr">
+      <c r="B179" s="30" t="inlineStr">
         <is>
           <t>다락원 마스터 시리즈(1~6, HSK 1~6)와 단원을 선택해요.</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="30" customHeight="1">
-      <c r="A154" s="27" t="n">
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B154" s="28" t="inlineStr">
+      <c r="B180" s="30" t="inlineStr">
         <is>
           <t>화면의 문장(한자 + 병음)을 따라 읽고, ‘원어민 발음 듣기’로 비교해요.</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="30" customHeight="1">
-      <c r="A155" s="27" t="n">
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B155" s="28" t="inlineStr">
+      <c r="B181" s="30" t="inlineStr">
         <is>
           <t>반복·느리게(0.85x) 기능으로 어려운 발음·성조를 연습해요.</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="24" customHeight="1">
-      <c r="A156" s="29" t="inlineStr">
+    <row r="182" ht="24" customHeight="1">
+      <c r="A182" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B156" s="30" t="inlineStr">
+      <c r="B182" s="32" t="inlineStr">
         <is>
           <t>한자와 병음(발음 표기)이 함께 나와 읽기 쉬워요.</t>
         </is>
       </c>
-      <c r="C156" s="31" t="n"/>
-      <c r="D156" s="31" t="n"/>
-      <c r="E156" s="31" t="n"/>
-      <c r="F156" s="31" t="n"/>
-    </row>
-    <row r="157" ht="24" customHeight="1">
-      <c r="A157" s="29" t="inlineStr">
+      <c r="C182" s="33" t="n"/>
+      <c r="D182" s="33" t="n"/>
+      <c r="E182" s="33" t="n"/>
+      <c r="F182" s="33" t="n"/>
+    </row>
+    <row r="183" ht="24" customHeight="1">
+      <c r="A183" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B157" s="30" t="inlineStr">
+      <c r="B183" s="32" t="inlineStr">
         <is>
           <t>AI가 음성을 인식해 원어민과 비교해줘요.</t>
         </is>
       </c>
-      <c r="C157" s="31" t="n"/>
-      <c r="D157" s="31" t="n"/>
-      <c r="E157" s="31" t="n"/>
-      <c r="F157" s="31" t="n"/>
-    </row>
-    <row r="158" ht="24" customHeight="1">
-      <c r="A158" s="29" t="inlineStr">
+      <c r="C183" s="33" t="n"/>
+      <c r="D183" s="33" t="n"/>
+      <c r="E183" s="33" t="n"/>
+      <c r="F183" s="33" t="n"/>
+    </row>
+    <row r="184" ht="24" customHeight="1">
+      <c r="A184" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B158" s="30" t="inlineStr">
+      <c r="B184" s="32" t="inlineStr">
         <is>
           <t>학습 게임 허브에서도 중국어를 지원해요.</t>
         </is>
       </c>
-      <c r="C158" s="31" t="n"/>
-      <c r="D158" s="31" t="n"/>
-      <c r="E158" s="31" t="n"/>
-      <c r="F158" s="31" t="n"/>
-    </row>
-    <row r="159" ht="30" customHeight="1">
-      <c r="A159" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 느리게로 듣고 또박또박 따라 하면 성조(4성)가 잘 잡혀요.</t>
-        </is>
-      </c>
-      <c r="B159" s="33" t="n"/>
-      <c r="C159" s="33" t="n"/>
-      <c r="D159" s="33" t="n"/>
-      <c r="E159" s="33" t="n"/>
-      <c r="F159" s="33" t="n"/>
-    </row>
-    <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="21" t="inlineStr">
-        <is>
-          <t>16  🌟 수업 중 칭찬 포인트 (이해·활용)  —  학생 동기부여·재등록에 연결</t>
-        </is>
-      </c>
-      <c r="B161" s="22" t="n"/>
-      <c r="C161" s="22" t="n"/>
-      <c r="D161" s="22" t="n"/>
-      <c r="E161" s="22" t="n"/>
-      <c r="F161" s="22" t="n"/>
-    </row>
-    <row r="162" ht="42" customHeight="1">
-      <c r="A162" s="23" t="inlineStr">
-        <is>
-          <t>📖 수업 중 교사가 학생에게 🌟 칭찬 포인트(+1P)를 즉석 지급하고, 수업 종료 별점(+10P)이 더해져 학생 총포인트로 쌓여요. 포인트는 상점·기프티콘 보상으로 이어져 학생 동기부여와 재등록에 도움이 돼요. 대리점는 이 흐름을 이해하고 성과에 활용해요.</t>
-        </is>
-      </c>
-      <c r="B162" s="24" t="n"/>
-      <c r="C162" s="24" t="n"/>
-      <c r="D162" s="24" t="n"/>
-      <c r="E162" s="24" t="n"/>
-      <c r="F162" s="24" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B163" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="30" customHeight="1">
-      <c r="A164" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B164" s="28" t="inlineStr">
-        <is>
-          <t>교사가 수업 중 학생 화면의 🌟 칭찬 버튼으로 +1P를 지급해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="30" customHeight="1">
-      <c r="A165" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B165" s="28" t="inlineStr">
-        <is>
-          <t>학생 🧺 포인트 바구니에 실시간 누적, 총 포인트에 합산돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B166" s="28" t="inlineStr">
-        <is>
-          <t>수업 종료 별점 평가로 학생은 +10P를 더 받아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="30" customHeight="1">
-      <c r="A167" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B167" s="28" t="inlineStr">
-        <is>
-          <t>포인트는 상점·룰렛·기프티콘 보상과 연결돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="24" customHeight="1">
-      <c r="A168" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B168" s="30" t="inlineStr">
-        <is>
-          <t>즉각 보상은 학생 참여·재등록에 긍정적이에요.</t>
-        </is>
-      </c>
-      <c r="C168" s="31" t="n"/>
-      <c r="D168" s="31" t="n"/>
-      <c r="E168" s="31" t="n"/>
-      <c r="F168" s="31" t="n"/>
-    </row>
-    <row r="169" ht="24" customHeight="1">
-      <c r="A169" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B169" s="30" t="inlineStr">
-        <is>
-          <t>우리 대리점 학생의 포인트·리워드 반응을 성과로 활용하세요.</t>
-        </is>
-      </c>
-      <c r="C169" s="31" t="n"/>
-      <c r="D169" s="31" t="n"/>
-      <c r="E169" s="31" t="n"/>
-      <c r="F169" s="31" t="n"/>
-    </row>
-    <row r="170" ht="26" customHeight="1">
-      <c r="A170" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 칭찬 포인트 지급은 교사가, 상점·리워드·기프티콘 정책은 본사(관리자)가 구성해요.</t>
-        </is>
-      </c>
-      <c r="B170" s="35" t="n"/>
-      <c r="C170" s="35" t="n"/>
-      <c r="D170" s="35" t="n"/>
-      <c r="E170" s="35" t="n"/>
-      <c r="F170" s="35" t="n"/>
-    </row>
-    <row r="171" ht="30" customHeight="1">
-      <c r="A171" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 칭찬 포인트가 잘 도는 반(교사)일수록 재등록률이 높은 경향이 있어요.</t>
-        </is>
-      </c>
-      <c r="B171" s="33" t="n"/>
-      <c r="C171" s="33" t="n"/>
-      <c r="D171" s="33" t="n"/>
-      <c r="E171" s="33" t="n"/>
-      <c r="F171" s="33" t="n"/>
-    </row>
-    <row r="173" ht="26" customHeight="1">
-      <c r="A173" s="21" t="inlineStr">
-        <is>
-          <t>17  📢 공지 스튜디오 (포스터 + 팝업)  —  공지·이벤트 포스터를 만들어 학생 앱 팝업으로</t>
-        </is>
-      </c>
-      <c r="B173" s="22" t="n"/>
-      <c r="C173" s="22" t="n"/>
-      <c r="D173" s="22" t="n"/>
-      <c r="E173" s="22" t="n"/>
-      <c r="F173" s="22" t="n"/>
-    </row>
-    <row r="174" ht="42" customHeight="1">
-      <c r="A174" s="23" t="inlineStr">
-        <is>
-          <t>📖 흩어져 있던 ‘포스터 만들기’와 ‘팝업 공지 관리’를 한 곳으로 통합한 기능이에요. ①만들기 탭에서 공지·이벤트 포스터를 디자인하고, 바로 ②게시·팝업 탭으로 넘겨 우리 대리점 학생 앱에 팝업으로 띄울 수 있어요.</t>
-        </is>
-      </c>
-      <c r="B174" s="24" t="n"/>
-      <c r="C174" s="24" t="n"/>
-      <c r="D174" s="24" t="n"/>
-      <c r="E174" s="24" t="n"/>
-      <c r="F174" s="24" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B175" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="30" customHeight="1">
-      <c r="A176" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B176" s="28" t="inlineStr">
-        <is>
-          <t>관리자 메뉴 알림 센터 → 📢 공지 스튜디오로 들어가요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="30" customHeight="1">
-      <c r="A177" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B177" s="28" t="inlineStr">
-        <is>
-          <t>①만들기 탭에서 문구·이미지·동영상으로 포스터를 꾸며요. (크기 조절·서버 저장·재사용 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="30" customHeight="1">
-      <c r="A178" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B178" s="28" t="inlineStr">
-        <is>
-          <t>완성한 포스터의 ‘📢 팝업으로 게시’ 를 누르면 ②게시·팝업 탭으로 자동 전환돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="30" customHeight="1">
-      <c r="A179" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B179" s="28" t="inlineStr">
-        <is>
-          <t>게시 탭에서 노출 기간·중단을 설정해 학생 앱 팝업으로 발행해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="24" customHeight="1">
-      <c r="A180" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B180" s="30" t="inlineStr">
-        <is>
-          <t>포스터 제작과 팝업 발행이 한 화면 2탭으로 이어져 헷갈리지 않아요.</t>
-        </is>
-      </c>
-      <c r="C180" s="31" t="n"/>
-      <c r="D180" s="31" t="n"/>
-      <c r="E180" s="31" t="n"/>
-      <c r="F180" s="31" t="n"/>
-    </row>
-    <row r="181" ht="24" customHeight="1">
-      <c r="A181" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B181" s="30" t="inlineStr">
-        <is>
-          <t>만든 포스터는 저장해두고 재사용할 수 있어요.</t>
-        </is>
-      </c>
-      <c r="C181" s="31" t="n"/>
-      <c r="D181" s="31" t="n"/>
-      <c r="E181" s="31" t="n"/>
-      <c r="F181" s="31" t="n"/>
-    </row>
-    <row r="182" ht="24" customHeight="1">
-      <c r="A182" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B182" s="30" t="inlineStr">
-        <is>
-          <t>AI 비서·사이드바 검색 어느 경로로 들어와도 올바른 탭이 열려요.</t>
-        </is>
-      </c>
-      <c r="C182" s="31" t="n"/>
-      <c r="D182" s="31" t="n"/>
-      <c r="E182" s="31" t="n"/>
-      <c r="F182" s="31" t="n"/>
-    </row>
-    <row r="183" ht="26" customHeight="1">
-      <c r="A183" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 기존 포스터·팝업 데이터는 그대로 유지돼요(통합만 됐고 삭제되지 않았어요).</t>
-        </is>
-      </c>
-      <c r="B183" s="35" t="n"/>
-      <c r="C183" s="35" t="n"/>
-      <c r="D183" s="35" t="n"/>
-      <c r="E183" s="35" t="n"/>
-      <c r="F183" s="35" t="n"/>
-    </row>
-    <row r="184" ht="30" customHeight="1">
-      <c r="A184" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 이벤트 홍보는 ‘만들기 → 바로 팝업 게시’ 흐름 한 번이면 끝나요.</t>
-        </is>
-      </c>
-      <c r="B184" s="33" t="n"/>
       <c r="C184" s="33" t="n"/>
       <c r="D184" s="33" t="n"/>
       <c r="E184" s="33" t="n"/>
       <c r="F184" s="33" t="n"/>
     </row>
-    <row r="186" ht="26" customHeight="1">
-      <c r="A186" s="21" t="inlineStr">
-        <is>
-          <t>18  🤖 AI 운영비서에게 시키기  —  “○○ 화면으로 가게 해줘” 한마디로 이동</t>
-        </is>
-      </c>
-      <c r="B186" s="22" t="n"/>
-      <c r="C186" s="22" t="n"/>
-      <c r="D186" s="22" t="n"/>
-      <c r="E186" s="22" t="n"/>
-      <c r="F186" s="22" t="n"/>
-    </row>
-    <row r="187" ht="42" customHeight="1">
-      <c r="A187" s="23" t="inlineStr">
-        <is>
-          <t>📖 상단 통합 검색창(또는 우하단 AI 운영비서) 에 하고 싶은 일을 자연스럽게 말하면, AI가 알아듣고 바로 그 화면으로 이동시켜줘요. 이제 ‘○○ 강사 스케줄로 가게 해줘’, ‘자동 스케줄링 열어줘’ 같은 이동 명령을 정확히 따라요.</t>
-        </is>
-      </c>
-      <c r="B187" s="24" t="n"/>
-      <c r="C187" s="24" t="n"/>
-      <c r="D187" s="24" t="n"/>
-      <c r="E187" s="24" t="n"/>
-      <c r="F187" s="24" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="25" t="inlineStr">
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 느리게로 듣고 또박또박 따라 하면 성조(4성)가 잘 잡혀요.</t>
+        </is>
+      </c>
+      <c r="B185" s="35" t="n"/>
+      <c r="C185" s="35" t="n"/>
+      <c r="D185" s="35" t="n"/>
+      <c r="E185" s="35" t="n"/>
+      <c r="F185" s="35" t="n"/>
+    </row>
+    <row r="187" ht="26" customHeight="1">
+      <c r="A187" s="21" t="inlineStr">
+        <is>
+          <t>16  🌟 수업 중 칭찬 포인트 (이해·활용)  —  학생 동기부여·재등록에 연결</t>
+        </is>
+      </c>
+      <c r="B187" s="22" t="n"/>
+      <c r="C187" s="22" t="n"/>
+      <c r="D187" s="22" t="n"/>
+      <c r="E187" s="22" t="n"/>
+      <c r="F187" s="22" t="n"/>
+    </row>
+    <row r="188" ht="42" customHeight="1">
+      <c r="A188" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업 중 교사가 학생에게 🌟 칭찬 포인트(+1P)를 즉석 지급하고, 수업 종료 별점(+10P)이 더해져 학생 총포인트로 쌓여요. 포인트는 상점·기프티콘 보상으로 이어져 학생 동기부여와 재등록에 도움이 돼요. 대리점는 이 흐름을 이해하고 성과에 활용해요.</t>
+        </is>
+      </c>
+      <c r="B188" s="24" t="n"/>
+      <c r="C188" s="24" t="n"/>
+      <c r="D188" s="24" t="n"/>
+      <c r="E188" s="24" t="n"/>
+      <c r="F188" s="24" t="n"/>
+    </row>
+    <row r="189" ht="24" customHeight="1">
+      <c r="A189" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 교사   ›   2 학생   ›   3 수업 종료 별점 평가   ›   4 상점·룰렛·기프티콘</t>
+        </is>
+      </c>
+      <c r="B189" s="26" t="n"/>
+      <c r="C189" s="26" t="n"/>
+      <c r="D189" s="26" t="n"/>
+      <c r="E189" s="26" t="n"/>
+      <c r="F189" s="26" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B188" s="26" t="inlineStr">
+      <c r="B190" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="30" customHeight="1">
-      <c r="A189" s="27" t="n">
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B189" s="28" t="inlineStr">
-        <is>
-          <t>상단 검색창에 명령을 입력하거나 🎤 마이크로 말해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="30" customHeight="1">
-      <c r="A190" s="27" t="n">
+      <c r="B191" s="30" t="inlineStr">
+        <is>
+          <t>교사가 수업 중 학생 화면의 🌟 칭찬 버튼으로 +1P를 지급해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B190" s="28" t="inlineStr">
-        <is>
-          <t>예: “김민지 강사 스케줄로 가게 해줘” → 주간 스케줄에서 해당 강사를 자동으로 찾아 열어줘요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="30" customHeight="1">
-      <c r="A191" s="27" t="n">
+      <c r="B192" s="30" t="inlineStr">
+        <is>
+          <t>학생 🧺 포인트 바구니에 실시간 누적, 총 포인트에 합산돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B191" s="28" t="inlineStr">
-        <is>
-          <t>예: “자동 스케줄링 열어줘”, “정산 화면으로” 처럼 메뉴 이동을 시켜요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="30" customHeight="1">
-      <c r="A192" s="27" t="n">
+      <c r="B193" s="30" t="inlineStr">
+        <is>
+          <t>수업 종료 별점 평가로 학생은 +10P를 더 받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B192" s="28" t="inlineStr">
-        <is>
-          <t>AI 응답 카드의 ‘지금 이동 →’ 을 누르면 해당 화면으로 넘어가요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="24" customHeight="1">
-      <c r="A193" s="29" t="inlineStr">
+      <c r="B194" s="30" t="inlineStr">
+        <is>
+          <t>포인트는 상점·룰렛·기프티콘 보상과 연결돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="24" customHeight="1">
+      <c r="A195" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B193" s="30" t="inlineStr">
-        <is>
-          <t>이동 명령은 확실히 이동하고, 설명만 하고 마는 일이 줄었어요.</t>
-        </is>
-      </c>
-      <c r="C193" s="31" t="n"/>
-      <c r="D193" s="31" t="n"/>
-      <c r="E193" s="31" t="n"/>
-      <c r="F193" s="31" t="n"/>
-    </row>
-    <row r="194" ht="24" customHeight="1">
-      <c r="A194" s="29" t="inlineStr">
+      <c r="B195" s="32" t="inlineStr">
+        <is>
+          <t>즉각 보상은 학생 참여·재등록에 긍정적이에요.</t>
+        </is>
+      </c>
+      <c r="C195" s="33" t="n"/>
+      <c r="D195" s="33" t="n"/>
+      <c r="E195" s="33" t="n"/>
+      <c r="F195" s="33" t="n"/>
+    </row>
+    <row r="196" ht="24" customHeight="1">
+      <c r="A196" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B194" s="30" t="inlineStr">
-        <is>
-          <t>강사 이름으로 스케줄을 검색하면 검색창 자동 채움 + 필터 + 스크롤까지 돼요.</t>
-        </is>
-      </c>
-      <c r="C194" s="31" t="n"/>
-      <c r="D194" s="31" t="n"/>
-      <c r="E194" s="31" t="n"/>
-      <c r="F194" s="31" t="n"/>
-    </row>
-    <row r="195" ht="24" customHeight="1">
-      <c r="A195" s="29" t="inlineStr">
+      <c r="B196" s="32" t="inlineStr">
+        <is>
+          <t>우리 대리점 학생의 포인트·리워드 반응을 성과로 활용하세요.</t>
+        </is>
+      </c>
+      <c r="C196" s="33" t="n"/>
+      <c r="D196" s="33" t="n"/>
+      <c r="E196" s="33" t="n"/>
+      <c r="F196" s="33" t="n"/>
+    </row>
+    <row r="197" ht="26" customHeight="1">
+      <c r="A197" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 칭찬 포인트 지급은 교사가, 상점·리워드·기프티콘 정책은 본사(관리자)가 구성해요.</t>
+        </is>
+      </c>
+      <c r="B197" s="37" t="n"/>
+      <c r="C197" s="37" t="n"/>
+      <c r="D197" s="37" t="n"/>
+      <c r="E197" s="37" t="n"/>
+      <c r="F197" s="37" t="n"/>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 칭찬 포인트가 잘 도는 반(교사)일수록 재등록률이 높은 경향이 있어요.</t>
+        </is>
+      </c>
+      <c r="B198" s="35" t="n"/>
+      <c r="C198" s="35" t="n"/>
+      <c r="D198" s="35" t="n"/>
+      <c r="E198" s="35" t="n"/>
+      <c r="F198" s="35" t="n"/>
+    </row>
+    <row r="200" ht="26" customHeight="1">
+      <c r="A200" s="21" t="inlineStr">
+        <is>
+          <t>17  📢 공지 스튜디오 (포스터 + 팝업)  —  공지·이벤트 포스터를 만들어 학생 앱 팝업으로</t>
+        </is>
+      </c>
+      <c r="B200" s="22" t="n"/>
+      <c r="C200" s="22" t="n"/>
+      <c r="D200" s="22" t="n"/>
+      <c r="E200" s="22" t="n"/>
+      <c r="F200" s="22" t="n"/>
+    </row>
+    <row r="201" ht="42" customHeight="1">
+      <c r="A201" s="23" t="inlineStr">
+        <is>
+          <t>📖 흩어져 있던 ‘포스터 만들기’와 ‘팝업 공지 관리’를 한 곳으로 통합한 기능이에요. ①만들기 탭에서 공지·이벤트 포스터를 디자인하고, 바로 ②게시·팝업 탭으로 넘겨 우리 대리점 학생 앱에 팝업으로 띄울 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B201" s="24" t="n"/>
+      <c r="C201" s="24" t="n"/>
+      <c r="D201" s="24" t="n"/>
+      <c r="E201" s="24" t="n"/>
+      <c r="F201" s="24" t="n"/>
+    </row>
+    <row r="202" ht="24" customHeight="1">
+      <c r="A202" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 알림 센터 → 📢 공지…   ›   2 ①만들기   ›   3 ‘📢 팝업으로 게시’   ›   4 노출 기간·중단</t>
+        </is>
+      </c>
+      <c r="B202" s="26" t="n"/>
+      <c r="C202" s="26" t="n"/>
+      <c r="D202" s="26" t="n"/>
+      <c r="E202" s="26" t="n"/>
+      <c r="F202" s="26" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B203" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="30" customHeight="1">
+      <c r="A204" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B204" s="30" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 알림 센터 → 📢 공지 스튜디오로 들어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="30" customHeight="1">
+      <c r="A205" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B205" s="30" t="inlineStr">
+        <is>
+          <t>①만들기 탭에서 문구·이미지·동영상으로 포스터를 꾸며요. (크기 조절·서버 저장·재사용 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="30" customHeight="1">
+      <c r="A206" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B206" s="30" t="inlineStr">
+        <is>
+          <t>완성한 포스터의 ‘📢 팝업으로 게시’ 를 누르면 ②게시·팝업 탭으로 자동 전환돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B207" s="30" t="inlineStr">
+        <is>
+          <t>게시 탭에서 노출 기간·중단을 설정해 학생 앱 팝업으로 발행해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="24" customHeight="1">
+      <c r="A208" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B195" s="30" t="inlineStr">
-        <is>
-          <t>데이터 조회·통계 질문에는 카드형 답변으로도 도와줘요.</t>
-        </is>
-      </c>
-      <c r="C195" s="31" t="n"/>
-      <c r="D195" s="31" t="n"/>
-      <c r="E195" s="31" t="n"/>
-      <c r="F195" s="31" t="n"/>
-    </row>
-    <row r="196" ht="26" customHeight="1">
-      <c r="A196" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · ‘등록·발송·변경’처럼 실제로 무언가를 바꾸는 명령은 한 번 더 확인해요(안전장치).</t>
-        </is>
-      </c>
-      <c r="B196" s="35" t="n"/>
-      <c r="C196" s="35" t="n"/>
-      <c r="D196" s="35" t="n"/>
-      <c r="E196" s="35" t="n"/>
-      <c r="F196" s="35" t="n"/>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 메뉴 이름이 기억나지 않을 땐 하고 싶은 일을 그대로 말해보세요 — 알아서 찾아가요.</t>
-        </is>
-      </c>
-      <c r="B197" s="33" t="n"/>
-      <c r="C197" s="33" t="n"/>
-      <c r="D197" s="33" t="n"/>
-      <c r="E197" s="33" t="n"/>
-      <c r="F197" s="33" t="n"/>
-    </row>
-    <row r="199" ht="26" customHeight="1">
-      <c r="A199" s="21" t="inlineStr">
-        <is>
-          <t>19  💬 자료실 카카오톡 링크 공유  —  영상·문서를 원본 화질 그대로 카톡으로</t>
-        </is>
-      </c>
-      <c r="B199" s="22" t="n"/>
-      <c r="C199" s="22" t="n"/>
-      <c r="D199" s="22" t="n"/>
-      <c r="E199" s="22" t="n"/>
-      <c r="F199" s="22" t="n"/>
-    </row>
-    <row r="200" ht="42" customHeight="1">
-      <c r="A200" s="23" t="inlineStr">
-        <is>
-          <t>📖 자료실의 설명서·영상마다 ‘💬 카톡 링크복사’ 버튼이 생겼어요. 카카오톡에 파일을 첨부하면 화질이 눌리지만, 링크로 보내면 원본 화질 그대로 재생돼요. 버튼 한 번으로 링크가 복사되니 학부모·강사 안내가 훨씬 쉬워요.</t>
-        </is>
-      </c>
-      <c r="B200" s="24" t="n"/>
-      <c r="C200" s="24" t="n"/>
-      <c r="D200" s="24" t="n"/>
-      <c r="E200" s="24" t="n"/>
-      <c r="F200" s="24" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B201" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="30" customHeight="1">
-      <c r="A202" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B202" s="28" t="inlineStr">
-        <is>
-          <t>관리자 자료실에서 공유할 파일 옆 💬 카톡 링크복사를 눌러요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="30" customHeight="1">
-      <c r="A203" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B203" s="28" t="inlineStr">
-        <is>
-          <t>카카오톡 대화방에 붙여넣기로 보내요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="30" customHeight="1">
-      <c r="A204" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B204" s="28" t="inlineStr">
-        <is>
-          <t>받는 사람은 링크를 눌러 원본 화질로 바로 보거나 내려받아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="24" customHeight="1">
-      <c r="A205" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B205" s="30" t="inlineStr">
-        <is>
-          <t>동영상은 링크 공유 = 원본 화질, 파일 첨부는 화질이 떨어져요.</t>
-        </is>
-      </c>
-      <c r="C205" s="31" t="n"/>
-      <c r="D205" s="31" t="n"/>
-      <c r="E205" s="31" t="n"/>
-      <c r="F205" s="31" t="n"/>
-    </row>
-    <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B206" s="30" t="inlineStr">
-        <is>
-          <t>설명서 PDF·PPT·영상 등 자료실 어디서나 같은 방식으로 공유돼요.</t>
-        </is>
-      </c>
-      <c r="C206" s="31" t="n"/>
-      <c r="D206" s="31" t="n"/>
-      <c r="E206" s="31" t="n"/>
-      <c r="F206" s="31" t="n"/>
-    </row>
-    <row r="207" ht="26" customHeight="1">
-      <c r="A207" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 링크를 받은 사람은 누구나 열 수 있어요. 내부용 자료는 공유 대상을 확인하세요.</t>
-        </is>
-      </c>
-      <c r="B207" s="35" t="n"/>
-      <c r="C207" s="35" t="n"/>
-      <c r="D207" s="35" t="n"/>
-      <c r="E207" s="35" t="n"/>
-      <c r="F207" s="35" t="n"/>
-    </row>
-    <row r="208" ht="30" customHeight="1">
-      <c r="A208" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 학부모 단체방에는 영상 설명서 링크 하나면 안내가 끝나요.</t>
-        </is>
-      </c>
-      <c r="B208" s="33" t="n"/>
+      <c r="B208" s="32" t="inlineStr">
+        <is>
+          <t>포스터 제작과 팝업 발행이 한 화면 2탭으로 이어져 헷갈리지 않아요.</t>
+        </is>
+      </c>
       <c r="C208" s="33" t="n"/>
       <c r="D208" s="33" t="n"/>
       <c r="E208" s="33" t="n"/>
       <c r="F208" s="33" t="n"/>
     </row>
-    <row r="210" ht="26" customHeight="1">
-      <c r="A210" s="21" t="inlineStr">
+    <row r="209" ht="24" customHeight="1">
+      <c r="A209" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B209" s="32" t="inlineStr">
+        <is>
+          <t>만든 포스터는 저장해두고 재사용할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C209" s="33" t="n"/>
+      <c r="D209" s="33" t="n"/>
+      <c r="E209" s="33" t="n"/>
+      <c r="F209" s="33" t="n"/>
+    </row>
+    <row r="210" ht="24" customHeight="1">
+      <c r="A210" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B210" s="32" t="inlineStr">
+        <is>
+          <t>AI 비서·사이드바 검색 어느 경로로 들어와도 올바른 탭이 열려요.</t>
+        </is>
+      </c>
+      <c r="C210" s="33" t="n"/>
+      <c r="D210" s="33" t="n"/>
+      <c r="E210" s="33" t="n"/>
+      <c r="F210" s="33" t="n"/>
+    </row>
+    <row r="211" ht="26" customHeight="1">
+      <c r="A211" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 기존 포스터·팝업 데이터는 그대로 유지돼요(통합만 됐고 삭제되지 않았어요).</t>
+        </is>
+      </c>
+      <c r="B211" s="37" t="n"/>
+      <c r="C211" s="37" t="n"/>
+      <c r="D211" s="37" t="n"/>
+      <c r="E211" s="37" t="n"/>
+      <c r="F211" s="37" t="n"/>
+    </row>
+    <row r="212" ht="30" customHeight="1">
+      <c r="A212" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 이벤트 홍보는 ‘만들기 → 바로 팝업 게시’ 흐름 한 번이면 끝나요.</t>
+        </is>
+      </c>
+      <c r="B212" s="35" t="n"/>
+      <c r="C212" s="35" t="n"/>
+      <c r="D212" s="35" t="n"/>
+      <c r="E212" s="35" t="n"/>
+      <c r="F212" s="35" t="n"/>
+    </row>
+    <row r="214" ht="26" customHeight="1">
+      <c r="A214" s="21" t="inlineStr">
+        <is>
+          <t>18  🤖 AI 운영비서에게 시키기  —  “○○ 화면으로 가게 해줘” 한마디로 이동</t>
+        </is>
+      </c>
+      <c r="B214" s="22" t="n"/>
+      <c r="C214" s="22" t="n"/>
+      <c r="D214" s="22" t="n"/>
+      <c r="E214" s="22" t="n"/>
+      <c r="F214" s="22" t="n"/>
+    </row>
+    <row r="215" ht="42" customHeight="1">
+      <c r="A215" s="23" t="inlineStr">
+        <is>
+          <t>📖 상단 통합 검색창(또는 우하단 AI 운영비서) 에 하고 싶은 일을 자연스럽게 말하면, AI가 알아듣고 바로 그 화면으로 이동시켜줘요. 이제 ‘○○ 강사 스케줄로 가게 해줘’, ‘자동 스케줄링 열어줘’ 같은 이동 명령을 정확히 따라요.</t>
+        </is>
+      </c>
+      <c r="B215" s="24" t="n"/>
+      <c r="C215" s="24" t="n"/>
+      <c r="D215" s="24" t="n"/>
+      <c r="E215" s="24" t="n"/>
+      <c r="F215" s="24" t="n"/>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="A216" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 검색창   ›   2 “김민지 강사 스케줄로…   ›   3 “자동 스케줄링 열어줘”…   ›   4 ‘지금 이동 →’</t>
+        </is>
+      </c>
+      <c r="B216" s="26" t="n"/>
+      <c r="C216" s="26" t="n"/>
+      <c r="D216" s="26" t="n"/>
+      <c r="E216" s="26" t="n"/>
+      <c r="F216" s="26" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B217" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="30" customHeight="1">
+      <c r="A218" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B218" s="30" t="inlineStr">
+        <is>
+          <t>상단 검색창에 명령을 입력하거나 🎤 마이크로 말해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="30" customHeight="1">
+      <c r="A219" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B219" s="30" t="inlineStr">
+        <is>
+          <t>예: “김민지 강사 스케줄로 가게 해줘” → 주간 스케줄에서 해당 강사를 자동으로 찾아 열어줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B220" s="30" t="inlineStr">
+        <is>
+          <t>예: “자동 스케줄링 열어줘”, “정산 화면으로” 처럼 메뉴 이동을 시켜요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B221" s="30" t="inlineStr">
+        <is>
+          <t>AI 응답 카드의 ‘지금 이동 →’ 을 누르면 해당 화면으로 넘어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="24" customHeight="1">
+      <c r="A222" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B222" s="32" t="inlineStr">
+        <is>
+          <t>이동 명령은 확실히 이동하고, 설명만 하고 마는 일이 줄었어요.</t>
+        </is>
+      </c>
+      <c r="C222" s="33" t="n"/>
+      <c r="D222" s="33" t="n"/>
+      <c r="E222" s="33" t="n"/>
+      <c r="F222" s="33" t="n"/>
+    </row>
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B223" s="32" t="inlineStr">
+        <is>
+          <t>강사 이름으로 스케줄을 검색하면 검색창 자동 채움 + 필터 + 스크롤까지 돼요.</t>
+        </is>
+      </c>
+      <c r="C223" s="33" t="n"/>
+      <c r="D223" s="33" t="n"/>
+      <c r="E223" s="33" t="n"/>
+      <c r="F223" s="33" t="n"/>
+    </row>
+    <row r="224" ht="24" customHeight="1">
+      <c r="A224" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B224" s="32" t="inlineStr">
+        <is>
+          <t>데이터 조회·통계 질문에는 카드형 답변으로도 도와줘요.</t>
+        </is>
+      </c>
+      <c r="C224" s="33" t="n"/>
+      <c r="D224" s="33" t="n"/>
+      <c r="E224" s="33" t="n"/>
+      <c r="F224" s="33" t="n"/>
+    </row>
+    <row r="225" ht="26" customHeight="1">
+      <c r="A225" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · ‘등록·발송·변경’처럼 실제로 무언가를 바꾸는 명령은 한 번 더 확인해요(안전장치).</t>
+        </is>
+      </c>
+      <c r="B225" s="37" t="n"/>
+      <c r="C225" s="37" t="n"/>
+      <c r="D225" s="37" t="n"/>
+      <c r="E225" s="37" t="n"/>
+      <c r="F225" s="37" t="n"/>
+    </row>
+    <row r="226" ht="30" customHeight="1">
+      <c r="A226" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 메뉴 이름이 기억나지 않을 땐 하고 싶은 일을 그대로 말해보세요 — 알아서 찾아가요.</t>
+        </is>
+      </c>
+      <c r="B226" s="35" t="n"/>
+      <c r="C226" s="35" t="n"/>
+      <c r="D226" s="35" t="n"/>
+      <c r="E226" s="35" t="n"/>
+      <c r="F226" s="35" t="n"/>
+    </row>
+    <row r="228" ht="26" customHeight="1">
+      <c r="A228" s="21" t="inlineStr">
+        <is>
+          <t>19  💬 자료실 카카오톡 링크 공유  —  영상·문서를 원본 화질 그대로 카톡으로</t>
+        </is>
+      </c>
+      <c r="B228" s="22" t="n"/>
+      <c r="C228" s="22" t="n"/>
+      <c r="D228" s="22" t="n"/>
+      <c r="E228" s="22" t="n"/>
+      <c r="F228" s="22" t="n"/>
+    </row>
+    <row r="229" ht="42" customHeight="1">
+      <c r="A229" s="23" t="inlineStr">
+        <is>
+          <t>📖 자료실의 설명서·영상마다 ‘💬 카톡 링크복사’ 버튼이 생겼어요. 카카오톡에 파일을 첨부하면 화질이 눌리지만, 링크로 보내면 원본 화질 그대로 재생돼요. 버튼 한 번으로 링크가 복사되니 학부모·강사 안내가 훨씬 쉬워요.</t>
+        </is>
+      </c>
+      <c r="B229" s="24" t="n"/>
+      <c r="C229" s="24" t="n"/>
+      <c r="D229" s="24" t="n"/>
+      <c r="E229" s="24" t="n"/>
+      <c r="F229" s="24" t="n"/>
+    </row>
+    <row r="230" ht="24" customHeight="1">
+      <c r="A230" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 자료실   ›   2 붙여넣기   ›   3 원본 화질</t>
+        </is>
+      </c>
+      <c r="B230" s="26" t="n"/>
+      <c r="C230" s="26" t="n"/>
+      <c r="D230" s="26" t="n"/>
+      <c r="E230" s="26" t="n"/>
+      <c r="F230" s="26" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B231" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="30" customHeight="1">
+      <c r="A232" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B232" s="30" t="inlineStr">
+        <is>
+          <t>관리자 자료실에서 공유할 파일 옆 💬 카톡 링크복사를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="30" customHeight="1">
+      <c r="A233" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B233" s="30" t="inlineStr">
+        <is>
+          <t>카카오톡 대화방에 붙여넣기로 보내요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B234" s="30" t="inlineStr">
+        <is>
+          <t>받는 사람은 링크를 눌러 원본 화질로 바로 보거나 내려받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="24" customHeight="1">
+      <c r="A235" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B235" s="32" t="inlineStr">
+        <is>
+          <t>동영상은 링크 공유 = 원본 화질, 파일 첨부는 화질이 떨어져요.</t>
+        </is>
+      </c>
+      <c r="C235" s="33" t="n"/>
+      <c r="D235" s="33" t="n"/>
+      <c r="E235" s="33" t="n"/>
+      <c r="F235" s="33" t="n"/>
+    </row>
+    <row r="236" ht="24" customHeight="1">
+      <c r="A236" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B236" s="32" t="inlineStr">
+        <is>
+          <t>설명서 PDF·PPT·영상 등 자료실 어디서나 같은 방식으로 공유돼요.</t>
+        </is>
+      </c>
+      <c r="C236" s="33" t="n"/>
+      <c r="D236" s="33" t="n"/>
+      <c r="E236" s="33" t="n"/>
+      <c r="F236" s="33" t="n"/>
+    </row>
+    <row r="237" ht="26" customHeight="1">
+      <c r="A237" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 링크를 받은 사람은 누구나 열 수 있어요. 내부용 자료는 공유 대상을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="B237" s="37" t="n"/>
+      <c r="C237" s="37" t="n"/>
+      <c r="D237" s="37" t="n"/>
+      <c r="E237" s="37" t="n"/>
+      <c r="F237" s="37" t="n"/>
+    </row>
+    <row r="238" ht="30" customHeight="1">
+      <c r="A238" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 학부모 단체방에는 영상 설명서 링크 하나면 안내가 끝나요.</t>
+        </is>
+      </c>
+      <c r="B238" s="35" t="n"/>
+      <c r="C238" s="35" t="n"/>
+      <c r="D238" s="35" t="n"/>
+      <c r="E238" s="35" t="n"/>
+      <c r="F238" s="35" t="n"/>
+    </row>
+    <row r="240" ht="26" customHeight="1">
+      <c r="A240" s="21" t="inlineStr">
         <is>
           <t>20  🧭 새로워진 관리자 화면  —  사이드바 접기 · 밝은 배경 · 선 아이콘</t>
         </is>
       </c>
-      <c r="B210" s="22" t="n"/>
-      <c r="C210" s="22" t="n"/>
-      <c r="D210" s="22" t="n"/>
-      <c r="E210" s="22" t="n"/>
-      <c r="F210" s="22" t="n"/>
-    </row>
-    <row r="211" ht="42" customHeight="1">
-      <c r="A211" s="23" t="inlineStr">
+      <c r="B240" s="22" t="n"/>
+      <c r="C240" s="22" t="n"/>
+      <c r="D240" s="22" t="n"/>
+      <c r="E240" s="22" t="n"/>
+      <c r="F240" s="22" t="n"/>
+    </row>
+    <row r="241" ht="42" customHeight="1">
+      <c r="A241" s="23" t="inlineStr">
         <is>
           <t>📖 관리자 화면이 눈이 편하고 넓게 바뀌었습니다. 왼쪽 메뉴는 ‹ 접기 버튼으로 아이콘만 남는 좁은 띠(레일) 로 접히고, 배경은 밝은 톤으로 통일됐어요. 메뉴 아이콘도 선(라인) 아이콘으로 정리해 글자가 잘 읽힙니다.</t>
         </is>
       </c>
-      <c r="B211" s="24" t="n"/>
-      <c r="C211" s="24" t="n"/>
-      <c r="D211" s="24" t="n"/>
-      <c r="E211" s="24" t="n"/>
-      <c r="F211" s="24" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="25" t="inlineStr">
+      <c r="B241" s="24" t="n"/>
+      <c r="C241" s="24" t="n"/>
+      <c r="D241" s="24" t="n"/>
+      <c r="E241" s="24" t="n"/>
+      <c r="F241" s="24" t="n"/>
+    </row>
+    <row r="242" ht="24" customHeight="1">
+      <c r="A242" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 ‹ 접기   ›   2 › 버튼   ›   3 다음 접속 때도 그대로…   ›   4 메뉴 검색</t>
+        </is>
+      </c>
+      <c r="B242" s="26" t="n"/>
+      <c r="C242" s="26" t="n"/>
+      <c r="D242" s="26" t="n"/>
+      <c r="E242" s="26" t="n"/>
+      <c r="F242" s="26" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B212" s="26" t="inlineStr">
+      <c r="B243" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="30" customHeight="1">
-      <c r="A213" s="27" t="n">
+    <row r="244" ht="30" customHeight="1">
+      <c r="A244" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B213" s="28" t="inlineStr">
+      <c r="B244" s="30" t="inlineStr">
         <is>
           <t>왼쪽 메뉴 맨 위의 ‹ 접기를 눌러요. 메뉴가 아이콘 띠로 줄어들며 본문이 넓어져요.</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="30" customHeight="1">
-      <c r="A214" s="27" t="n">
+    <row r="245" ht="30" customHeight="1">
+      <c r="A245" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B214" s="28" t="inlineStr">
+      <c r="B245" s="30" t="inlineStr">
         <is>
           <t>다시 펼치려면 같은 자리의 › 버튼을 눌러요.</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="30" customHeight="1">
-      <c r="A215" s="27" t="n">
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B215" s="28" t="inlineStr">
+      <c r="B246" s="30" t="inlineStr">
         <is>
           <t>접은 상태는 다음 접속 때도 그대로 기억됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="30" customHeight="1">
-      <c r="A216" s="27" t="n">
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B216" s="28" t="inlineStr">
+      <c r="B247" s="30" t="inlineStr">
         <is>
           <t>메뉴가 많아 찾기 어려우면 위쪽 메뉴 검색에 이름을 쳐 보세요.</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="24" customHeight="1">
-      <c r="A217" s="29" t="inlineStr">
+    <row r="248" ht="24" customHeight="1">
+      <c r="A248" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B217" s="30" t="inlineStr">
+      <c r="B248" s="32" t="inlineStr">
         <is>
           <t>표·목록이 많은 화면에서 가로 공간이 크게 늘어나요.</t>
         </is>
       </c>
-      <c r="C217" s="31" t="n"/>
-      <c r="D217" s="31" t="n"/>
-      <c r="E217" s="31" t="n"/>
-      <c r="F217" s="31" t="n"/>
-    </row>
-    <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="29" t="inlineStr">
+      <c r="C248" s="33" t="n"/>
+      <c r="D248" s="33" t="n"/>
+      <c r="E248" s="33" t="n"/>
+      <c r="F248" s="33" t="n"/>
+    </row>
+    <row r="249" ht="24" customHeight="1">
+      <c r="A249" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B218" s="30" t="inlineStr">
+      <c r="B249" s="32" t="inlineStr">
         <is>
           <t>하위 메뉴 15장까지 밝은 테마로 통일돼 화면 간 색 차이가 사라졌어요.</t>
         </is>
       </c>
-      <c r="C218" s="31" t="n"/>
-      <c r="D218" s="31" t="n"/>
-      <c r="E218" s="31" t="n"/>
-      <c r="F218" s="31" t="n"/>
-    </row>
-    <row r="219" ht="24" customHeight="1">
-      <c r="A219" s="29" t="inlineStr">
+      <c r="C249" s="33" t="n"/>
+      <c r="D249" s="33" t="n"/>
+      <c r="E249" s="33" t="n"/>
+      <c r="F249" s="33" t="n"/>
+    </row>
+    <row r="250" ht="24" customHeight="1">
+      <c r="A250" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B219" s="30" t="inlineStr">
+      <c r="B250" s="32" t="inlineStr">
         <is>
           <t>저사양 PC에서도 버벅이지 않도록 접기 애니메이션을 없앴습니다.</t>
         </is>
       </c>
-      <c r="C219" s="31" t="n"/>
-      <c r="D219" s="31" t="n"/>
-      <c r="E219" s="31" t="n"/>
-      <c r="F219" s="31" t="n"/>
-    </row>
-    <row r="220" ht="30" customHeight="1">
-      <c r="A220" s="32" t="inlineStr">
+      <c r="C250" s="33" t="n"/>
+      <c r="D250" s="33" t="n"/>
+      <c r="E250" s="33" t="n"/>
+      <c r="F250" s="33" t="n"/>
+    </row>
+    <row r="251" ht="30" customHeight="1">
+      <c r="A251" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 정산·급여처럼 표가 넓은 화면은 접어 놓고 보면 훨씬 편합니다.</t>
         </is>
       </c>
-      <c r="B220" s="33" t="n"/>
-      <c r="C220" s="33" t="n"/>
-      <c r="D220" s="33" t="n"/>
-      <c r="E220" s="33" t="n"/>
-      <c r="F220" s="33" t="n"/>
-    </row>
-    <row r="222" ht="26" customHeight="1">
-      <c r="A222" s="21" t="inlineStr">
+      <c r="B251" s="35" t="n"/>
+      <c r="C251" s="35" t="n"/>
+      <c r="D251" s="35" t="n"/>
+      <c r="E251" s="35" t="n"/>
+      <c r="F251" s="35" t="n"/>
+    </row>
+    <row r="253" ht="26" customHeight="1">
+      <c r="A253" s="21" t="inlineStr">
         <is>
           <t>21  🌐 화면 언어가 자동으로 맞춰져요  —  해외 스태프·강사는 영어로 시작</t>
         </is>
       </c>
-      <c r="B222" s="22" t="n"/>
-      <c r="C222" s="22" t="n"/>
-      <c r="D222" s="22" t="n"/>
-      <c r="E222" s="22" t="n"/>
-      <c r="F222" s="22" t="n"/>
-    </row>
-    <row r="223" ht="42" customHeight="1">
-      <c r="A223" s="23" t="inlineStr">
+      <c r="B253" s="22" t="n"/>
+      <c r="C253" s="22" t="n"/>
+      <c r="D253" s="22" t="n"/>
+      <c r="E253" s="22" t="n"/>
+      <c r="F253" s="22" t="n"/>
+    </row>
+    <row r="254" ht="42" customHeight="1">
+      <c r="A254" s="23" t="inlineStr">
         <is>
           <t>📖 필리핀 강사와 해외 스태프가 처음부터 영어 화면으로 시작합니다. 계정의 국적 정보를 기준으로 화면 언어가 정해지고, 강사 계정은 이름·이전 선택과 무관하게 항상 영어로 뜹니다. 물론 상단 🌐 EN / KR 버튼으로 언제든 직접 바꿀 수 있어요.</t>
         </is>
       </c>
-      <c r="B223" s="24" t="n"/>
-      <c r="C223" s="24" t="n"/>
-      <c r="D223" s="24" t="n"/>
-      <c r="E223" s="24" t="n"/>
-      <c r="F223" s="24" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="25" t="inlineStr">
+      <c r="B254" s="24" t="n"/>
+      <c r="C254" s="24" t="n"/>
+      <c r="D254" s="24" t="n"/>
+      <c r="E254" s="24" t="n"/>
+      <c r="F254" s="24" t="n"/>
+    </row>
+    <row r="255" ht="24" customHeight="1">
+      <c r="A255" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 국적   ›   2 🌐 EN / KR   ›   3 그 계정에만   ›   4 영어판으로 함께</t>
+        </is>
+      </c>
+      <c r="B255" s="26" t="n"/>
+      <c r="C255" s="26" t="n"/>
+      <c r="D255" s="26" t="n"/>
+      <c r="E255" s="26" t="n"/>
+      <c r="F255" s="26" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B224" s="26" t="inlineStr">
+      <c r="B256" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="30" customHeight="1">
-      <c r="A225" s="27" t="n">
+    <row r="257" ht="30" customHeight="1">
+      <c r="A257" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B225" s="28" t="inlineStr">
+      <c r="B257" s="30" t="inlineStr">
         <is>
           <t>계정에 국적이 등록돼 있으면 로그인할 때 자동으로 맞는 언어가 뜹니다.</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="30" customHeight="1">
-      <c r="A226" s="27" t="n">
+    <row r="258" ht="30" customHeight="1">
+      <c r="A258" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B226" s="28" t="inlineStr">
+      <c r="B258" s="30" t="inlineStr">
         <is>
           <t>직접 바꾸려면 상단의 🌐 EN / KR 버튼을 눌러요.</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="30" customHeight="1">
-      <c r="A227" s="27" t="n">
+    <row r="259" ht="30" customHeight="1">
+      <c r="A259" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B227" s="28" t="inlineStr">
+      <c r="B259" s="30" t="inlineStr">
         <is>
           <t>직접 고른 언어는 그 계정에만 저장돼요 — 같은 PC를 여러 명이 써도 섞이지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="30" customHeight="1">
-      <c r="A228" s="27" t="n">
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B228" s="28" t="inlineStr">
+      <c r="B260" s="30" t="inlineStr">
         <is>
           <t>강사용 안내 슬라이드·안내서도 영어판으로 함께 바뀝니다.</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="24" customHeight="1">
-      <c r="A229" s="29" t="inlineStr">
+    <row r="261" ht="24" customHeight="1">
+      <c r="A261" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B229" s="30" t="inlineStr">
+      <c r="B261" s="32" t="inlineStr">
         <is>
           <t>강사 계정은 무조건 영어 — 한국어 화면 때문에 헤매는 일이 없어요.</t>
         </is>
       </c>
-      <c r="C229" s="31" t="n"/>
-      <c r="D229" s="31" t="n"/>
-      <c r="E229" s="31" t="n"/>
-      <c r="F229" s="31" t="n"/>
-    </row>
-    <row r="230" ht="24" customHeight="1">
-      <c r="A230" s="29" t="inlineStr">
+      <c r="C261" s="33" t="n"/>
+      <c r="D261" s="33" t="n"/>
+      <c r="E261" s="33" t="n"/>
+      <c r="F261" s="33" t="n"/>
+    </row>
+    <row r="262" ht="24" customHeight="1">
+      <c r="A262" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B230" s="30" t="inlineStr">
+      <c r="B262" s="32" t="inlineStr">
         <is>
           <t>이름에 붙은 한글 직함 때문에 영문 이름 계정이 한국어로 뜨던 문제도 고쳤어요.</t>
         </is>
       </c>
-      <c r="C230" s="31" t="n"/>
-      <c r="D230" s="31" t="n"/>
-      <c r="E230" s="31" t="n"/>
-      <c r="F230" s="31" t="n"/>
-    </row>
-    <row r="231" ht="24" customHeight="1">
-      <c r="A231" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B231" s="30" t="inlineStr">
-        <is>
-          <t>언어 선택이 계정별로 분리돼 해외 계정이 남의 선택에 덮이지 않아요.</t>
-        </is>
-      </c>
-      <c r="C231" s="31" t="n"/>
-      <c r="D231" s="31" t="n"/>
-      <c r="E231" s="31" t="n"/>
-      <c r="F231" s="31" t="n"/>
-    </row>
-    <row r="232" ht="26" customHeight="1">
-      <c r="A232" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 국적이 비어 있는 계정은 기존 방식(이름·아이디 규칙)으로 판단합니다. 강사 등록 시 국적을 꼭 넣어 주세요.</t>
-        </is>
-      </c>
-      <c r="B232" s="35" t="n"/>
-      <c r="C232" s="35" t="n"/>
-      <c r="D232" s="35" t="n"/>
-      <c r="E232" s="35" t="n"/>
-      <c r="F232" s="35" t="n"/>
-    </row>
-    <row r="233" ht="30" customHeight="1">
-      <c r="A233" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 새 강사를 등록할 때 국적을 함께 입력하면 첫 로그인부터 영어 화면으로 시작해 문의가 줄어듭니다.</t>
-        </is>
-      </c>
-      <c r="B233" s="33" t="n"/>
-      <c r="C233" s="33" t="n"/>
-      <c r="D233" s="33" t="n"/>
-      <c r="E233" s="33" t="n"/>
-      <c r="F233" s="33" t="n"/>
-    </row>
-    <row r="235" ht="26" customHeight="1">
-      <c r="A235" s="21" t="inlineStr">
-        <is>
-          <t>22  💳 수강 등록 · 결제 → 수업 자동 생성  —  결제 확정되면 회차 전량이 자동으로 잡힙니다</t>
-        </is>
-      </c>
-      <c r="B235" s="22" t="n"/>
-      <c r="C235" s="22" t="n"/>
-      <c r="D235" s="22" t="n"/>
-      <c r="E235" s="22" t="n"/>
-      <c r="F235" s="22" t="n"/>
-    </row>
-    <row r="236" ht="42" customHeight="1">
-      <c r="A236" s="23" t="inlineStr">
-        <is>
-          <t>📖 수강신청 화면에서 학생이 강사·요일·시간을 고르고 결제하면, 결제 확정 시점에 수업 회차가 전량 자동 생성됩니다. 예전처럼 결제 확인 후 사람이 일일이 시간표를 넣던 작업이 사라졌어요. 같은 시간에 이미 잡힌 수업이 있으면 결제 전에 충돌을 감지해 알려 줍니다.</t>
-        </is>
-      </c>
-      <c r="B236" s="24" t="n"/>
-      <c r="C236" s="24" t="n"/>
-      <c r="D236" s="24" t="n"/>
-      <c r="E236" s="24" t="n"/>
-      <c r="F236" s="24" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B237" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="30" customHeight="1">
-      <c r="A238" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B238" s="28" t="inlineStr">
-        <is>
-          <t>학생·학부모에게 수강신청 링크를 안내해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="30" customHeight="1">
-      <c r="A239" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B239" s="28" t="inlineStr">
-        <is>
-          <t>학생이 강사 → 수업 옵션(주 횟수·기간·수업 길이) → 요일·시간 순으로 고릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="30" customHeight="1">
-      <c r="A240" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B240" s="28" t="inlineStr">
-        <is>
-          <t>시간 확인이 통과돼야 결제 버튼이 열립니다(충돌 시 결제 불가).</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="30" customHeight="1">
-      <c r="A241" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B241" s="28" t="inlineStr">
-        <is>
-          <t>결제가 확정되면 회차가 한꺼번에 생성됩니다. 관리자 화면 수업 목록에서 확인해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="30" customHeight="1">
-      <c r="A242" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B242" s="28" t="inlineStr">
-        <is>
-          <t>본사 단가·할인율은 단가표 화면에서 관리합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="24" customHeight="1">
-      <c r="A243" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B243" s="30" t="inlineStr">
-        <is>
-          <t>멱등 처리돼서 결제 알림이 중복 들어와도 회차가 두 번 생기지 않아요.</t>
-        </is>
-      </c>
-      <c r="C243" s="31" t="n"/>
-      <c r="D243" s="31" t="n"/>
-      <c r="E243" s="31" t="n"/>
-      <c r="F243" s="31" t="n"/>
-    </row>
-    <row r="244" ht="24" customHeight="1">
-      <c r="A244" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B244" s="30" t="inlineStr">
-        <is>
-          <t>공휴일·기존 수업과 겹치면 뒤로 밀어서 회차 수를 채웁니다.</t>
-        </is>
-      </c>
-      <c r="C244" s="31" t="n"/>
-      <c r="D244" s="31" t="n"/>
-      <c r="E244" s="31" t="n"/>
-      <c r="F244" s="31" t="n"/>
-    </row>
-    <row r="245" ht="24" customHeight="1">
-      <c r="A245" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B245" s="30" t="inlineStr">
-        <is>
-          <t>기간 할인(6개월 -5% · 12개월 -10%)이 금액에 자동 반영됩니다.</t>
-        </is>
-      </c>
-      <c r="C245" s="31" t="n"/>
-      <c r="D245" s="31" t="n"/>
-      <c r="E245" s="31" t="n"/>
-      <c r="F245" s="31" t="n"/>
-    </row>
-    <row r="246" ht="26" customHeight="1">
-      <c r="A246" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 현재는 1단계(등록 → 결제 → 회차 자동 생성) 까지 열려 있습니다. 이후 단계는 순차 반영 예정입니다.</t>
-        </is>
-      </c>
-      <c r="B246" s="35" t="n"/>
-      <c r="C246" s="35" t="n"/>
-      <c r="D246" s="35" t="n"/>
-      <c r="E246" s="35" t="n"/>
-      <c r="F246" s="35" t="n"/>
-    </row>
-    <row r="247" ht="30" customHeight="1">
-      <c r="A247" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
-        </is>
-      </c>
-      <c r="B247" s="33" t="n"/>
-      <c r="C247" s="33" t="n"/>
-      <c r="D247" s="33" t="n"/>
-      <c r="E247" s="33" t="n"/>
-      <c r="F247" s="33" t="n"/>
-    </row>
-    <row r="249" ht="26" customHeight="1">
-      <c r="A249" s="21" t="inlineStr">
-        <is>
-          <t>23  🗂️ 강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)  —  찾기 쉬운 명부 · 한눈에 보는 상세</t>
-        </is>
-      </c>
-      <c r="B249" s="22" t="n"/>
-      <c r="C249" s="22" t="n"/>
-      <c r="D249" s="22" t="n"/>
-      <c r="E249" s="22" t="n"/>
-      <c r="F249" s="22" t="n"/>
-    </row>
-    <row r="250" ht="42" customHeight="1">
-      <c r="A250" s="23" t="inlineStr">
-        <is>
-          <t>📖 강사 관리 화면이 찾기 쉽고 보기 편하게 정리됐어요. 흩어져 있던 메뉴를 네 묶음으로 그룹지어 사이드바에 담았고, 강사 명부 위에는 구분·상태·그룹 드롭다운 필터와 적용된 필터 칩이 생겼어요. 강사를 누르면 프로필·급여·평가 탭으로 나뉜 상세 화면이 열리고, 매니저 배지와 재직 상태(재직·휴직·퇴사) 가 한눈에 표시돼요.</t>
-        </is>
-      </c>
-      <c r="B250" s="24" t="n"/>
-      <c r="C250" s="24" t="n"/>
-      <c r="D250" s="24" t="n"/>
-      <c r="E250" s="24" t="n"/>
-      <c r="F250" s="24" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="25" t="inlineStr">
-        <is>
-          <t>단계</t>
-        </is>
-      </c>
-      <c r="B251" s="26" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="30" customHeight="1">
-      <c r="A252" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B252" s="28" t="inlineStr">
-        <is>
-          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요).</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="30" customHeight="1">
-      <c r="A253" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B253" s="28" t="inlineStr">
-        <is>
-          <t>명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B254" s="28" t="inlineStr">
-        <is>
-          <t>적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="30" customHeight="1">
-      <c r="A255" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B255" s="28" t="inlineStr">
-        <is>
-          <t>강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="30" customHeight="1">
-      <c r="A256" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B256" s="28" t="inlineStr">
-        <is>
-          <t>급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="24" customHeight="1">
-      <c r="A257" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B257" s="30" t="inlineStr">
-        <is>
-          <t>매니저는 배지로 구분되고, 재직 상태가 재직·휴직·퇴사 3가지로 표시돼요.</t>
-        </is>
-      </c>
-      <c r="C257" s="31" t="n"/>
-      <c r="D257" s="31" t="n"/>
-      <c r="E257" s="31" t="n"/>
-      <c r="F257" s="31" t="n"/>
-    </row>
-    <row r="258" ht="24" customHeight="1">
-      <c r="A258" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B258" s="30" t="inlineStr">
-        <is>
-          <t>이름이 비어도 아이디로 대체 표기돼 빈칸이 없어요.</t>
-        </is>
-      </c>
-      <c r="C258" s="31" t="n"/>
-      <c r="D258" s="31" t="n"/>
-      <c r="E258" s="31" t="n"/>
-      <c r="F258" s="31" t="n"/>
-    </row>
-    <row r="259" ht="24" customHeight="1">
-      <c r="A259" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B259" s="30" t="inlineStr">
-        <is>
-          <t>상세 탭은 기존 API를 재사용해 빠르게 뜨고, 화면은 한/영 병기예요.</t>
-        </is>
-      </c>
-      <c r="C259" s="31" t="n"/>
-      <c r="D259" s="31" t="n"/>
-      <c r="E259" s="31" t="n"/>
-      <c r="F259" s="31" t="n"/>
-    </row>
-    <row r="260" ht="24" customHeight="1">
-      <c r="A260" s="29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="B260" s="30" t="inlineStr">
-        <is>
-          <t>중복이던 급여 입구를 정리하고 버그 접수는 별도 시스템으로 옮겼어요.</t>
-        </is>
-      </c>
-      <c r="C260" s="31" t="n"/>
-      <c r="D260" s="31" t="n"/>
-      <c r="E260" s="31" t="n"/>
-      <c r="F260" s="31" t="n"/>
-    </row>
-    <row r="261" ht="26" customHeight="1">
-      <c r="A261" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
-        </is>
-      </c>
-      <c r="B261" s="35" t="n"/>
-      <c r="C261" s="35" t="n"/>
-      <c r="D261" s="35" t="n"/>
-      <c r="E261" s="35" t="n"/>
-      <c r="F261" s="35" t="n"/>
-    </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="32" t="inlineStr">
-        <is>
-          <t>💡 꿀팁 · 강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
-        </is>
-      </c>
-      <c r="B262" s="33" t="n"/>
       <c r="C262" s="33" t="n"/>
       <c r="D262" s="33" t="n"/>
       <c r="E262" s="33" t="n"/>
       <c r="F262" s="33" t="n"/>
     </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B263" s="32" t="inlineStr">
+        <is>
+          <t>언어 선택이 계정별로 분리돼 해외 계정이 남의 선택에 덮이지 않아요.</t>
+        </is>
+      </c>
+      <c r="C263" s="33" t="n"/>
+      <c r="D263" s="33" t="n"/>
+      <c r="E263" s="33" t="n"/>
+      <c r="F263" s="33" t="n"/>
+    </row>
     <row r="264" ht="26" customHeight="1">
-      <c r="A264" s="21" t="inlineStr">
+      <c r="A264" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 국적이 비어 있는 계정은 기존 방식(이름·아이디 규칙)으로 판단합니다. 강사 등록 시 국적을 꼭 넣어 주세요.</t>
+        </is>
+      </c>
+      <c r="B264" s="37" t="n"/>
+      <c r="C264" s="37" t="n"/>
+      <c r="D264" s="37" t="n"/>
+      <c r="E264" s="37" t="n"/>
+      <c r="F264" s="37" t="n"/>
+    </row>
+    <row r="265" ht="30" customHeight="1">
+      <c r="A265" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 새 강사를 등록할 때 국적을 함께 입력하면 첫 로그인부터 영어 화면으로 시작해 문의가 줄어듭니다.</t>
+        </is>
+      </c>
+      <c r="B265" s="35" t="n"/>
+      <c r="C265" s="35" t="n"/>
+      <c r="D265" s="35" t="n"/>
+      <c r="E265" s="35" t="n"/>
+      <c r="F265" s="35" t="n"/>
+    </row>
+    <row r="267" ht="26" customHeight="1">
+      <c r="A267" s="21" t="inlineStr">
+        <is>
+          <t>22  💳 수강 등록 · 결제 → 수업 자동 생성  —  결제 확정되면 회차 전량이 자동으로 잡힙니다</t>
+        </is>
+      </c>
+      <c r="B267" s="22" t="n"/>
+      <c r="C267" s="22" t="n"/>
+      <c r="D267" s="22" t="n"/>
+      <c r="E267" s="22" t="n"/>
+      <c r="F267" s="22" t="n"/>
+    </row>
+    <row r="268" ht="42" customHeight="1">
+      <c r="A268" s="23" t="inlineStr">
+        <is>
+          <t>📖 수강신청 화면에서 학생이 강사·요일·시간을 고르고 결제하면, 결제 확정 시점에 수업 회차가 전량 자동 생성됩니다. 예전처럼 결제 확인 후 사람이 일일이 시간표를 넣던 작업이 사라졌어요. 같은 시간에 이미 잡힌 수업이 있으면 결제 전에 충돌을 감지해 알려 줍니다.</t>
+        </is>
+      </c>
+      <c r="B268" s="24" t="n"/>
+      <c r="C268" s="24" t="n"/>
+      <c r="D268" s="24" t="n"/>
+      <c r="E268" s="24" t="n"/>
+      <c r="F268" s="24" t="n"/>
+    </row>
+    <row r="269" ht="24" customHeight="1">
+      <c r="A269" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 수강신청 링크   ›   2 강사 → 수업 옵션(주…   ›   3 시간 확인   ›   4 회차가 한꺼번에 생성   ›   5 단가표 화면</t>
+        </is>
+      </c>
+      <c r="B269" s="26" t="n"/>
+      <c r="C269" s="26" t="n"/>
+      <c r="D269" s="26" t="n"/>
+      <c r="E269" s="26" t="n"/>
+      <c r="F269" s="26" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B271" s="30" t="inlineStr">
+        <is>
+          <t>학생·학부모에게 수강신청 링크를 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="30" customHeight="1">
+      <c r="A272" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B272" s="30" t="inlineStr">
+        <is>
+          <t>학생이 강사 → 수업 옵션(주 횟수·기간·수업 길이) → 요일·시간 순으로 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="30" customHeight="1">
+      <c r="A273" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B273" s="30" t="inlineStr">
+        <is>
+          <t>시간 확인이 통과돼야 결제 버튼이 열립니다(충돌 시 결제 불가).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="30" customHeight="1">
+      <c r="A274" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B274" s="30" t="inlineStr">
+        <is>
+          <t>결제가 확정되면 회차가 한꺼번에 생성됩니다. 관리자 화면 수업 목록에서 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B275" s="30" t="inlineStr">
+        <is>
+          <t>본사 단가·할인율은 단가표 화면에서 관리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="24" customHeight="1">
+      <c r="A276" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B276" s="32" t="inlineStr">
+        <is>
+          <t>멱등 처리돼서 결제 알림이 중복 들어와도 회차가 두 번 생기지 않아요.</t>
+        </is>
+      </c>
+      <c r="C276" s="33" t="n"/>
+      <c r="D276" s="33" t="n"/>
+      <c r="E276" s="33" t="n"/>
+      <c r="F276" s="33" t="n"/>
+    </row>
+    <row r="277" ht="24" customHeight="1">
+      <c r="A277" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B277" s="32" t="inlineStr">
+        <is>
+          <t>공휴일·기존 수업과 겹치면 뒤로 밀어서 회차 수를 채웁니다.</t>
+        </is>
+      </c>
+      <c r="C277" s="33" t="n"/>
+      <c r="D277" s="33" t="n"/>
+      <c r="E277" s="33" t="n"/>
+      <c r="F277" s="33" t="n"/>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B278" s="32" t="inlineStr">
+        <is>
+          <t>기간 할인(6개월 -5% · 12개월 -10%)이 금액에 자동 반영됩니다.</t>
+        </is>
+      </c>
+      <c r="C278" s="33" t="n"/>
+      <c r="D278" s="33" t="n"/>
+      <c r="E278" s="33" t="n"/>
+      <c r="F278" s="33" t="n"/>
+    </row>
+    <row r="279" ht="26" customHeight="1">
+      <c r="A279" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 현재는 1단계(등록 → 결제 → 회차 자동 생성) 까지 열려 있습니다. 이후 단계는 순차 반영 예정입니다.</t>
+        </is>
+      </c>
+      <c r="B279" s="37" t="n"/>
+      <c r="C279" s="37" t="n"/>
+      <c r="D279" s="37" t="n"/>
+      <c r="E279" s="37" t="n"/>
+      <c r="F279" s="37" t="n"/>
+    </row>
+    <row r="280" ht="30" customHeight="1">
+      <c r="A280" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
+        </is>
+      </c>
+      <c r="B280" s="35" t="n"/>
+      <c r="C280" s="35" t="n"/>
+      <c r="D280" s="35" t="n"/>
+      <c r="E280" s="35" t="n"/>
+      <c r="F280" s="35" t="n"/>
+    </row>
+    <row r="282" ht="26" customHeight="1">
+      <c r="A282" s="21" t="inlineStr">
+        <is>
+          <t>23  🗂️ 강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)  —  찾기 쉬운 명부 · 한눈에 보는 상세</t>
+        </is>
+      </c>
+      <c r="B282" s="22" t="n"/>
+      <c r="C282" s="22" t="n"/>
+      <c r="D282" s="22" t="n"/>
+      <c r="E282" s="22" t="n"/>
+      <c r="F282" s="22" t="n"/>
+    </row>
+    <row r="283" ht="42" customHeight="1">
+      <c r="A283" s="23" t="inlineStr">
+        <is>
+          <t>📖 강사 관리 화면이 찾기 쉽고 보기 편하게 정리됐어요. 흩어져 있던 메뉴를 네 묶음으로 그룹지어 사이드바에 담았고, 강사 명부 위에는 구분·상태·그룹 드롭다운 필터와 적용된 필터 칩이 생겼어요. 강사를 누르면 프로필·급여·평가 탭으로 나뉜 상세 화면이 열리고, 매니저 배지와 재직 상태(재직·휴직·퇴사) 가 한눈에 표시돼요.</t>
+        </is>
+      </c>
+      <c r="B283" s="24" t="n"/>
+      <c r="C283" s="24" t="n"/>
+      <c r="D283" s="24" t="n"/>
+      <c r="E283" s="24" t="n"/>
+      <c r="F283" s="24" t="n"/>
+    </row>
+    <row r="284" ht="24" customHeight="1">
+      <c r="A284" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 강사 통합   ›   2 상태·그룹 드롭다운   ›   3 칩   ›   4 프로필 / 급여 / 평가   ›   5 급여·평가 탭의 요약 숫…</t>
+        </is>
+      </c>
+      <c r="B284" s="26" t="n"/>
+      <c r="C284" s="26" t="n"/>
+      <c r="D284" s="26" t="n"/>
+      <c r="E284" s="26" t="n"/>
+      <c r="F284" s="26" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B285" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="30" customHeight="1">
+      <c r="A286" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B286" s="30" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="30" customHeight="1">
+      <c r="A287" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B287" s="30" t="inlineStr">
+        <is>
+          <t>명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="30" customHeight="1">
+      <c r="A288" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B288" s="30" t="inlineStr">
+        <is>
+          <t>적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="30" customHeight="1">
+      <c r="A289" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B289" s="30" t="inlineStr">
+        <is>
+          <t>강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="30" customHeight="1">
+      <c r="A290" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B290" s="30" t="inlineStr">
+        <is>
+          <t>급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="24" customHeight="1">
+      <c r="A291" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B291" s="32" t="inlineStr">
+        <is>
+          <t>매니저는 배지로 구분되고, 재직 상태가 재직·휴직·퇴사 3가지로 표시돼요.</t>
+        </is>
+      </c>
+      <c r="C291" s="33" t="n"/>
+      <c r="D291" s="33" t="n"/>
+      <c r="E291" s="33" t="n"/>
+      <c r="F291" s="33" t="n"/>
+    </row>
+    <row r="292" ht="24" customHeight="1">
+      <c r="A292" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B292" s="32" t="inlineStr">
+        <is>
+          <t>이름이 비어도 아이디로 대체 표기돼 빈칸이 없어요.</t>
+        </is>
+      </c>
+      <c r="C292" s="33" t="n"/>
+      <c r="D292" s="33" t="n"/>
+      <c r="E292" s="33" t="n"/>
+      <c r="F292" s="33" t="n"/>
+    </row>
+    <row r="293" ht="24" customHeight="1">
+      <c r="A293" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B293" s="32" t="inlineStr">
+        <is>
+          <t>상세 탭은 기존 API를 재사용해 빠르게 뜨고, 화면은 한/영 병기예요.</t>
+        </is>
+      </c>
+      <c r="C293" s="33" t="n"/>
+      <c r="D293" s="33" t="n"/>
+      <c r="E293" s="33" t="n"/>
+      <c r="F293" s="33" t="n"/>
+    </row>
+    <row r="294" ht="24" customHeight="1">
+      <c r="A294" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B294" s="32" t="inlineStr">
+        <is>
+          <t>중복이던 급여 입구를 정리하고 버그 접수는 별도 시스템으로 옮겼어요.</t>
+        </is>
+      </c>
+      <c r="C294" s="33" t="n"/>
+      <c r="D294" s="33" t="n"/>
+      <c r="E294" s="33" t="n"/>
+      <c r="F294" s="33" t="n"/>
+    </row>
+    <row r="295" ht="26" customHeight="1">
+      <c r="A295" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
+        </is>
+      </c>
+      <c r="B295" s="37" t="n"/>
+      <c r="C295" s="37" t="n"/>
+      <c r="D295" s="37" t="n"/>
+      <c r="E295" s="37" t="n"/>
+      <c r="F295" s="37" t="n"/>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+      <c r="B296" s="35" t="n"/>
+      <c r="C296" s="35" t="n"/>
+      <c r="D296" s="35" t="n"/>
+      <c r="E296" s="35" t="n"/>
+      <c r="F296" s="35" t="n"/>
+    </row>
+    <row r="298" ht="26" customHeight="1">
+      <c r="A298" s="21" t="inlineStr">
         <is>
           <t>24  🌟 학부모 월간 성적표 (오각형) 발송  —  5축 그래프 성적표를 미리보고 링크로</t>
         </is>
       </c>
-      <c r="B264" s="22" t="n"/>
-      <c r="C264" s="22" t="n"/>
-      <c r="D264" s="22" t="n"/>
-      <c r="E264" s="22" t="n"/>
-      <c r="F264" s="22" t="n"/>
-    </row>
-    <row r="265" ht="42" customHeight="1">
-      <c r="A265" s="23" t="inlineStr">
+      <c r="B298" s="22" t="n"/>
+      <c r="C298" s="22" t="n"/>
+      <c r="D298" s="22" t="n"/>
+      <c r="E298" s="22" t="n"/>
+      <c r="F298" s="22" t="n"/>
+    </row>
+    <row r="299" ht="42" customHeight="1">
+      <c r="A299" s="23" t="inlineStr">
         <is>
           <t>📖 학부모에게 보내는 월간 성적표가 오각형 5축 그래프로 새로워졌어요. 발음·유창성 / 어휘 / 문장 구성력 / 수업 태도 / 참여도 를 한눈에 보여 주고, 출결·판단력·담임의 한마디가 함께 담깁니다. 관리자·교사는 학생 ID와 월을 넣어 미리보기한 뒤 카카오톡 링크로 보냅니다.</t>
         </is>
       </c>
-      <c r="B265" s="24" t="n"/>
-      <c r="C265" s="24" t="n"/>
-      <c r="D265" s="24" t="n"/>
-      <c r="E265" s="24" t="n"/>
-      <c r="F265" s="24" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="25" t="inlineStr">
+      <c r="B299" s="24" t="n"/>
+      <c r="C299" s="24" t="n"/>
+      <c r="D299" s="24" t="n"/>
+      <c r="E299" s="24" t="n"/>
+      <c r="F299" s="24" t="n"/>
+    </row>
+    <row r="300" ht="24" customHeight="1">
+      <c r="A300" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 월간 리포트   ›   2 학생 ID   ›   3 오각형과 담임의 한마디를…   ›   4 ?uid=학생ID&amp;per…</t>
+        </is>
+      </c>
+      <c r="B300" s="26" t="n"/>
+      <c r="C300" s="26" t="n"/>
+      <c r="D300" s="26" t="n"/>
+      <c r="E300" s="26" t="n"/>
+      <c r="F300" s="26" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="27" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B266" s="26" t="inlineStr">
+      <c r="B301" s="28" t="inlineStr">
         <is>
           <t>할 일</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="30" customHeight="1">
-      <c r="A267" s="27" t="n">
+    <row r="302" ht="30" customHeight="1">
+      <c r="A302" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B267" s="28" t="inlineStr">
+      <c r="B302" s="30" t="inlineStr">
         <is>
           <t>월간 리포트 화면을 열어요.</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="30" customHeight="1">
-      <c r="A268" s="27" t="n">
+    <row r="303" ht="30" customHeight="1">
+      <c r="A303" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B268" s="28" t="inlineStr">
+      <c r="B303" s="30" t="inlineStr">
         <is>
           <t>학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요.</t>
         </is>
       </c>
     </row>
-    <row r="269" ht="30" customHeight="1">
-      <c r="A269" s="27" t="n">
+    <row r="304" ht="30" customHeight="1">
+      <c r="A304" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B269" s="28" t="inlineStr">
+      <c r="B304" s="30" t="inlineStr">
         <is>
           <t>오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요.</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="30" customHeight="1">
-      <c r="A270" s="27" t="n">
+    <row r="305" ht="30" customHeight="1">
+      <c r="A305" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B270" s="28" t="inlineStr">
+      <c r="B305" s="30" t="inlineStr">
         <is>
           <t>주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
         </is>
       </c>
     </row>
-    <row r="271" ht="24" customHeight="1">
-      <c r="A271" s="29" t="inlineStr">
+    <row r="306" ht="24" customHeight="1">
+      <c r="A306" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B271" s="30" t="inlineStr">
+      <c r="B306" s="32" t="inlineStr">
         <is>
           <t>실제 기록이 있는 축만 채워져 신뢰할 수 있어요.</t>
         </is>
       </c>
-      <c r="C271" s="31" t="n"/>
-      <c r="D271" s="31" t="n"/>
-      <c r="E271" s="31" t="n"/>
-      <c r="F271" s="31" t="n"/>
-    </row>
-    <row r="272" ht="24" customHeight="1">
-      <c r="A272" s="29" t="inlineStr">
+      <c r="C306" s="33" t="n"/>
+      <c r="D306" s="33" t="n"/>
+      <c r="E306" s="33" t="n"/>
+      <c r="F306" s="33" t="n"/>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B272" s="30" t="inlineStr">
+      <c r="B307" s="32" t="inlineStr">
         <is>
           <t>2개월 주기로 정리해 학부모 피로 없이 변화를 전달해요.</t>
         </is>
       </c>
-      <c r="C272" s="31" t="n"/>
-      <c r="D272" s="31" t="n"/>
-      <c r="E272" s="31" t="n"/>
-      <c r="F272" s="31" t="n"/>
-    </row>
-    <row r="273" ht="24" customHeight="1">
-      <c r="A273" s="29" t="inlineStr">
+      <c r="C307" s="33" t="n"/>
+      <c r="D307" s="33" t="n"/>
+      <c r="E307" s="33" t="n"/>
+      <c r="F307" s="33" t="n"/>
+    </row>
+    <row r="308" ht="24" customHeight="1">
+      <c r="A308" s="31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="B273" s="30" t="inlineStr">
+      <c r="B308" s="32" t="inlineStr">
         <is>
           <t>인쇄/PDF 버튼으로 상담용 종이 성적표도 즉시 만들 수 있어요.</t>
         </is>
       </c>
-      <c r="C273" s="31" t="n"/>
-      <c r="D273" s="31" t="n"/>
-      <c r="E273" s="31" t="n"/>
-      <c r="F273" s="31" t="n"/>
-    </row>
-    <row r="274" ht="26" customHeight="1">
-      <c r="A274" s="34" t="inlineStr">
-        <is>
-          <t>⚠️ 알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
-        </is>
-      </c>
-      <c r="B274" s="35" t="n"/>
-      <c r="C274" s="35" t="n"/>
-      <c r="D274" s="35" t="n"/>
-      <c r="E274" s="35" t="n"/>
-      <c r="F274" s="35" t="n"/>
-    </row>
-    <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="32" t="inlineStr">
+      <c r="C308" s="33" t="n"/>
+      <c r="D308" s="33" t="n"/>
+      <c r="E308" s="33" t="n"/>
+      <c r="F308" s="33" t="n"/>
+    </row>
+    <row r="309" ht="26" customHeight="1">
+      <c r="A309" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
+        </is>
+      </c>
+      <c r="B309" s="37" t="n"/>
+      <c r="C309" s="37" t="n"/>
+      <c r="D309" s="37" t="n"/>
+      <c r="E309" s="37" t="n"/>
+      <c r="F309" s="37" t="n"/>
+    </row>
+    <row r="310" ht="30" customHeight="1">
+      <c r="A310" s="34" t="inlineStr">
         <is>
           <t>💡 꿀팁 · 상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
         </is>
       </c>
-      <c r="B275" s="33" t="n"/>
-      <c r="C275" s="33" t="n"/>
-      <c r="D275" s="33" t="n"/>
-      <c r="E275" s="33" t="n"/>
-      <c r="F275" s="33" t="n"/>
+      <c r="B310" s="35" t="n"/>
+      <c r="C310" s="35" t="n"/>
+      <c r="D310" s="35" t="n"/>
+      <c r="E310" s="35" t="n"/>
+      <c r="F310" s="35" t="n"/>
+    </row>
+    <row r="312" ht="26" customHeight="1">
+      <c r="A312" s="21" t="inlineStr">
+        <is>
+          <t>25  📅 학부모 주간 리포트 (재등록을 잇는 무기)  —  경쟁사가 못 보여 주는 ‘성장의 증거’를 매주</t>
+        </is>
+      </c>
+      <c r="B312" s="22" t="n"/>
+      <c r="C312" s="22" t="n"/>
+      <c r="D312" s="22" t="n"/>
+      <c r="E312" s="22" t="n"/>
+      <c r="F312" s="22" t="n"/>
+    </row>
+    <row r="313" ht="42" customHeight="1">
+      <c r="A313" s="23" t="inlineStr">
+        <is>
+          <t>📖 아이의 한 주 활동(출석·AI 친구 대화·판단력·정복한 단어·발음)을 담아 학부모에게 보내는 리포트입니다. 목적은 분명합니다 — 경쟁사가 보여 주지 못하는 ‘성장의 증거’를 매주 전달해 재등록으로 잇는 것입니다. 관리자 화면에서 미리보기 → 테스트 발송 → 대상 집계 → 발송 로그를 모두 확인할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="B313" s="24" t="n"/>
+      <c r="C313" s="24" t="n"/>
+      <c r="D313" s="24" t="n"/>
+      <c r="E313" s="24" t="n"/>
+      <c r="F313" s="24" t="n"/>
+    </row>
+    <row r="314" ht="24" customHeight="1">
+      <c r="A314" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 📅 학부모 주간 리포트   ›   2 미리보기   ›   3 이 학부모에게 실제 발송   ›   4 발송 대상 집계   ›   5 최근 발송 로그</t>
+        </is>
+      </c>
+      <c r="B314" s="26" t="n"/>
+      <c r="C314" s="26" t="n"/>
+      <c r="D314" s="26" t="n"/>
+      <c r="E314" s="26" t="n"/>
+      <c r="F314" s="26" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B315" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="30" customHeight="1">
+      <c r="A316" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B316" s="30" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 📅 학부모 주간 리포트를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="30" customHeight="1">
+      <c r="A317" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B317" s="30" t="inlineStr">
+        <is>
+          <t>학생 ID를 넣고 미리보기로 내용을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="30" customHeight="1">
+      <c r="A318" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B318" s="30" t="inlineStr">
+        <is>
+          <t>필요하면 이 학부모에게 실제 발송으로 한 명에게만 테스트해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B319" s="30" t="inlineStr">
+        <is>
+          <t>발송 대상 집계로 지금 받을 수 있는 학생 수(전화번호 등록자)를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="30" customHeight="1">
+      <c r="A320" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B320" s="30" t="inlineStr">
+        <is>
+          <t>최근 발송 로그로 실제로 나간 기록을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="24" customHeight="1">
+      <c r="A321" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B321" s="32" t="inlineStr">
+        <is>
+          <t>리포트에 담기는 것: 📅 출석 일수 · 🔥 연속 출석 · 🤖 AI 대화 · 📚 정복 단어 · 🧠 판단력 · 🎤 발음.</t>
+        </is>
+      </c>
+      <c r="C321" s="33" t="n"/>
+      <c r="D321" s="33" t="n"/>
+      <c r="E321" s="33" t="n"/>
+      <c r="F321" s="33" t="n"/>
+    </row>
+    <row r="322" ht="24" customHeight="1">
+      <c r="A322" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B322" s="32" t="inlineStr">
+        <is>
+          <t>전화번호가 등록된 학생만 받을 수 있어요 — 집계 화면이 미등록 인원을 함께 알려 줍니다.</t>
+        </is>
+      </c>
+      <c r="C322" s="33" t="n"/>
+      <c r="D322" s="33" t="n"/>
+      <c r="E322" s="33" t="n"/>
+      <c r="F322" s="33" t="n"/>
+    </row>
+    <row r="323" ht="24" customHeight="1">
+      <c r="A323" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B323" s="32" t="inlineStr">
+        <is>
+          <t>매주 금요일 저녁 자동 발송(크론) 이 준비돼 있습니다.</t>
+        </is>
+      </c>
+      <c r="C323" s="33" t="n"/>
+      <c r="D323" s="33" t="n"/>
+      <c r="E323" s="33" t="n"/>
+      <c r="F323" s="33" t="n"/>
+    </row>
+    <row r="324" ht="26" customHeight="1">
+      <c r="A324" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 🔴 전체 자동 발송은 기본으로 꺼져 있습니다. 관리자가 KV 스위치를 켠 뒤에만 실제 문자가 나갑니다 — 실수로 29,000명에게 발송되는 사고를 막기 위한 안전장치입니다. 알림톡 템플릿 승인과 대표 결정 뒤에 켜세요.</t>
+        </is>
+      </c>
+      <c r="B324" s="37" t="n"/>
+      <c r="C324" s="37" t="n"/>
+      <c r="D324" s="37" t="n"/>
+      <c r="E324" s="37" t="n"/>
+      <c r="F324" s="37" t="n"/>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 먼저 미리보기 → 한 명 테스트 발송까지만 해 보세요. 문구가 확정되면 그때 전체 스위치를 켜면 됩니다.</t>
+        </is>
+      </c>
+      <c r="B325" s="35" t="n"/>
+      <c r="C325" s="35" t="n"/>
+      <c r="D325" s="35" t="n"/>
+      <c r="E325" s="35" t="n"/>
+      <c r="F325" s="35" t="n"/>
+    </row>
+    <row r="327" ht="26" customHeight="1">
+      <c r="A327" s="21" t="inlineStr">
+        <is>
+          <t>26  🏠 홈 첫 화면 개편 (처음 온 학부모 · 기존 회원 자동 분리)  —  상담 전화가 줄고 체험 신청이 늘어나는 구조</t>
+        </is>
+      </c>
+      <c r="B327" s="22" t="n"/>
+      <c r="C327" s="22" t="n"/>
+      <c r="D327" s="22" t="n"/>
+      <c r="E327" s="22" t="n"/>
+      <c r="F327" s="22" t="n"/>
+    </row>
+    <row r="328" ht="42" customHeight="1">
+      <c r="A328" s="23" t="inlineStr">
+        <is>
+          <t>📖 홈페이지 첫 화면(히어로)이 보는 사람에 따라 두 가지로 나뉘어 표시됩니다. 처음 온 학부모에게는 &lt;b&gt;무료 체험 신청&lt;/b&gt;이 가장 큰 버튼으로, 이미 로그인한 회원에게는 &lt;b&gt;수업 입장&lt;/b&gt;이 가장 큰 버튼으로 뜹니다. 경쟁사 4곳(캠블리키즈·민병철유폰·엔구·링글)을 실제로 확인한 결과 모두 첫 버튼이 신규 상담·체험 신청이었고, 이를 반영한 개편입니다.</t>
+        </is>
+      </c>
+      <c r="B328" s="24" t="n"/>
+      <c r="C328" s="24" t="n"/>
+      <c r="D328" s="24" t="n"/>
+      <c r="E328" s="24" t="n"/>
+      <c r="F328" s="24" t="n"/>
+    </row>
+    <row r="329" ht="24" customHeight="1">
+      <c r="A329" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 홈 주소   ›   2 무료 체험 신청 · 강사…   ›   3 수업 입장 · AI와 친…   ›   4 홈 주소 그대로</t>
+        </is>
+      </c>
+      <c r="B329" s="26" t="n"/>
+      <c r="C329" s="26" t="n"/>
+      <c r="D329" s="26" t="n"/>
+      <c r="E329" s="26" t="n"/>
+      <c r="F329" s="26" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B330" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="30" customHeight="1">
+      <c r="A331" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B331" s="30" t="inlineStr">
+        <is>
+          <t>새 창(시크릿 모드)으로 홈 주소를 열어 비회원 화면을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="A332" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B332" s="30" t="inlineStr">
+        <is>
+          <t>무료 체험 신청 · 강사 둘러보기 두 버튼이 크게 보이는지 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="30" customHeight="1">
+      <c r="A333" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B333" s="30" t="inlineStr">
+        <is>
+          <t>로그인한 뒤 같은 화면을 열면 수업 입장 · AI와 친구하기로 바뀌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="30" customHeight="1">
+      <c r="A334" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B334" s="30" t="inlineStr">
+        <is>
+          <t>홍보물·문자에는 홈 주소 그대로 넣으면 됩니다 — 별도 랜딩페이지가 필요 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="24" customHeight="1">
+      <c r="A335" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B335" s="32" t="inlineStr">
+        <is>
+          <t>페이지를 새로 만들지 않았어요. 같은 주소가 로그인 여부만 보고 알아서 바뀝니다.</t>
+        </is>
+      </c>
+      <c r="C335" s="33" t="n"/>
+      <c r="D335" s="33" t="n"/>
+      <c r="E335" s="33" t="n"/>
+      <c r="F335" s="33" t="n"/>
+    </row>
+    <row r="336" ht="24" customHeight="1">
+      <c r="A336" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B336" s="32" t="inlineStr">
+        <is>
+          <t>비회원 화면에도 작은 ‘수업 입장’ 링크를 남겼어요 — 기기를 바꾸거나 로그인이 풀린 기존 학생이 수업에 못 들어가는 사고를 막습니다.</t>
+        </is>
+      </c>
+      <c r="C336" s="33" t="n"/>
+      <c r="D336" s="33" t="n"/>
+      <c r="E336" s="33" t="n"/>
+      <c r="F336" s="33" t="n"/>
+    </row>
+    <row r="337" ht="24" customHeight="1">
+      <c r="A337" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B337" s="32" t="inlineStr">
+        <is>
+          <t>판정에 실패하면 무조건 비회원 화면으로 떨어집니다 — 화면이 비는 일이 없어요.</t>
+        </is>
+      </c>
+      <c r="C337" s="33" t="n"/>
+      <c r="D337" s="33" t="n"/>
+      <c r="E337" s="33" t="n"/>
+      <c r="F337" s="33" t="n"/>
+    </row>
+    <row r="338" ht="24" customHeight="1">
+      <c r="A338" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B338" s="32" t="inlineStr">
+        <is>
+          <t>깜빡임이 없습니다. 화면이 그려지기 전에 판정이 끝나요.</t>
+        </is>
+      </c>
+      <c r="C338" s="33" t="n"/>
+      <c r="D338" s="33" t="n"/>
+      <c r="E338" s="33" t="n"/>
+      <c r="F338" s="33" t="n"/>
+    </row>
+    <row r="339" ht="26" customHeight="1">
+      <c r="A339" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 비회원 화면의 작은 ‘수업 입장’ 링크는 절대 빼면 안 됩니다. 로그인이 30일 만에 만료되거나 기기를 바꾼 기존 회원도 이 화면을 보기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="B339" s="37" t="n"/>
+      <c r="C339" s="37" t="n"/>
+      <c r="D339" s="37" t="n"/>
+      <c r="E339" s="37" t="n"/>
+      <c r="F339" s="37" t="n"/>
+    </row>
+    <row r="340" ht="30" customHeight="1">
+      <c r="A340" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 체험 신청 전환을 보고 싶다면 시크릿 창으로 홈에 들어가 보세요. 학부모가 처음 보는 화면이 그대로 나옵니다.</t>
+        </is>
+      </c>
+      <c r="B340" s="35" t="n"/>
+      <c r="C340" s="35" t="n"/>
+      <c r="D340" s="35" t="n"/>
+      <c r="E340" s="35" t="n"/>
+      <c r="F340" s="35" t="n"/>
+    </row>
+    <row r="342" ht="26" customHeight="1">
+      <c r="A342" s="21" t="inlineStr">
+        <is>
+          <t>27  ⚡ 관리자 화면이 훨씬 빨라졌어요  —  누르면 멈추던 현상 제거</t>
+        </is>
+      </c>
+      <c r="B342" s="22" t="n"/>
+      <c r="C342" s="22" t="n"/>
+      <c r="D342" s="22" t="n"/>
+      <c r="E342" s="22" t="n"/>
+      <c r="F342" s="22" t="n"/>
+    </row>
+    <row r="343" ht="42" customHeight="1">
+      <c r="A343" s="23" t="inlineStr">
+        <is>
+          <t>📖 관리자 화면에서 무엇을 누르면 잠깐 멈추던 현상을 없앴습니다. 원인은 누른 기능이 아니라, 글자를 읽기 좋게 만들어 주는 보정 기능이 접혀 있는 카드까지 매번 다시 계산하고 있었던 것입니다. 접힌 카드는 건너뛰고, 이미 처리한 곳은 다시 만지지 않도록 고쳤습니다.</t>
+        </is>
+      </c>
+      <c r="B343" s="24" t="n"/>
+      <c r="C343" s="24" t="n"/>
+      <c r="D343" s="24" t="n"/>
+      <c r="E343" s="24" t="n"/>
+      <c r="F343" s="24" t="n"/>
+    </row>
+    <row r="344" ht="24" customHeight="1">
+      <c r="A344" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 관리자 화면을 평소처럼…   ›   2 멈춤 없이 바로 열리는지   ›   3 새로고침(Ctrl+F5)</t>
+        </is>
+      </c>
+      <c r="B344" s="26" t="n"/>
+      <c r="C344" s="26" t="n"/>
+      <c r="D344" s="26" t="n"/>
+      <c r="E344" s="26" t="n"/>
+      <c r="F344" s="26" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B345" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="30" customHeight="1">
+      <c r="A346" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B346" s="30" t="inlineStr">
+        <is>
+          <t>관리자 화면을 평소처럼 사용해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="30" customHeight="1">
+      <c r="A347" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B347" s="30" t="inlineStr">
+        <is>
+          <t>메뉴·카드를 눌렀을 때 멈춤 없이 바로 열리는지 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="30" customHeight="1">
+      <c r="A348" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B348" s="30" t="inlineStr">
+        <is>
+          <t>느리게 느껴지면 브라우저에서 새로고침(Ctrl+F5) 을 한 번 해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="24" customHeight="1">
+      <c r="A349" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B349" s="32" t="inlineStr">
+        <is>
+          <t>클릭 시 멈춤 396ms → 57ms, 대기 중 부하 366ms → 0ms 로 줄었습니다.</t>
+        </is>
+      </c>
+      <c r="C349" s="33" t="n"/>
+      <c r="D349" s="33" t="n"/>
+      <c r="E349" s="33" t="n"/>
+      <c r="F349" s="33" t="n"/>
+    </row>
+    <row r="350" ht="24" customHeight="1">
+      <c r="A350" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B350" s="32" t="inlineStr">
+        <is>
+          <t>화면 모양과 색은 전혀 바뀌지 않았습니다 — 속도만 좋아졌어요.</t>
+        </is>
+      </c>
+      <c r="C350" s="33" t="n"/>
+      <c r="D350" s="33" t="n"/>
+      <c r="E350" s="33" t="n"/>
+      <c r="F350" s="33" t="n"/>
+    </row>
+    <row r="351" ht="24" customHeight="1">
+      <c r="A351" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B351" s="32" t="inlineStr">
+        <is>
+          <t>카드가 많은 화면(강사·학생 목록)일수록 체감이 큽니다.</t>
+        </is>
+      </c>
+      <c r="C351" s="33" t="n"/>
+      <c r="D351" s="33" t="n"/>
+      <c r="E351" s="33" t="n"/>
+      <c r="F351" s="33" t="n"/>
+    </row>
+    <row r="352" ht="26" customHeight="1">
+      <c r="A352" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 브라우저에 옛 화면이 남아 있으면 개선이 바로 느껴지지 않을 수 있어요. 강력 새로고침(Ctrl+F5) 을 한 번 해 주세요.</t>
+        </is>
+      </c>
+      <c r="B352" s="37" t="n"/>
+      <c r="C352" s="37" t="n"/>
+      <c r="D352" s="37" t="n"/>
+      <c r="E352" s="37" t="n"/>
+      <c r="F352" s="37" t="n"/>
+    </row>
+    <row r="353" ht="30" customHeight="1">
+      <c r="A353" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 그래도 느리다면 브라우저 탭을 너무 많이 열어 두지 않았는지 확인해 보세요.</t>
+        </is>
+      </c>
+      <c r="B353" s="35" t="n"/>
+      <c r="C353" s="35" t="n"/>
+      <c r="D353" s="35" t="n"/>
+      <c r="E353" s="35" t="n"/>
+      <c r="F353" s="35" t="n"/>
+    </row>
+    <row r="355" ht="26" customHeight="1">
+      <c r="A355" s="21" t="inlineStr">
+        <is>
+          <t>28  🔎 학원 검색칸 (이름으로 바로 찾기)  —  목록을 훑지 않고 바로</t>
+        </is>
+      </c>
+      <c r="B355" s="22" t="n"/>
+      <c r="C355" s="22" t="n"/>
+      <c r="D355" s="22" t="n"/>
+      <c r="E355" s="22" t="n"/>
+      <c r="F355" s="22" t="n"/>
+    </row>
+    <row r="356" ht="42" customHeight="1">
+      <c r="A356" s="23" t="inlineStr">
+        <is>
+          <t>📖 학원(지사·대리점) 목록에서 이름을 입력해 바로 찾을 수 있는 검색칸이 생겼습니다. 학원 수가 많아 목록을 위아래로 훑어야 했던 불편을 없앴습니다.</t>
+        </is>
+      </c>
+      <c r="B356" s="24" t="n"/>
+      <c r="C356" s="24" t="n"/>
+      <c r="D356" s="24" t="n"/>
+      <c r="E356" s="24" t="n"/>
+      <c r="F356" s="24" t="n"/>
+    </row>
+    <row r="357" ht="24" customHeight="1">
+      <c r="A357" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 학원 목록   ›   2 검색칸   ›   3 해당 학원만   ›   4 전체 목록</t>
+        </is>
+      </c>
+      <c r="B357" s="26" t="n"/>
+      <c r="C357" s="26" t="n"/>
+      <c r="D357" s="26" t="n"/>
+      <c r="E357" s="26" t="n"/>
+      <c r="F357" s="26" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B358" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="30" customHeight="1">
+      <c r="A359" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B359" s="30" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 학원 목록 화면을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="30" customHeight="1">
+      <c r="A360" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B360" s="30" t="inlineStr">
+        <is>
+          <t>목록 위 검색칸에 학원 이름 일부를 입력해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="30" customHeight="1">
+      <c r="A361" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B361" s="30" t="inlineStr">
+        <is>
+          <t>입력하는 즉시 해당 학원만 목록에 남아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="30" customHeight="1">
+      <c r="A362" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B362" s="30" t="inlineStr">
+        <is>
+          <t>검색칸을 비우면 전체 목록으로 돌아와요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="24" customHeight="1">
+      <c r="A363" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B363" s="32" t="inlineStr">
+        <is>
+          <t>이름 일부만 입력해도 찾아집니다.</t>
+        </is>
+      </c>
+      <c r="C363" s="33" t="n"/>
+      <c r="D363" s="33" t="n"/>
+      <c r="E363" s="33" t="n"/>
+      <c r="F363" s="33" t="n"/>
+    </row>
+    <row r="364" ht="24" customHeight="1">
+      <c r="A364" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B364" s="32" t="inlineStr">
+        <is>
+          <t>기존 목록·기능은 그대로이고 찾는 방법만 추가됐습니다.</t>
+        </is>
+      </c>
+      <c r="C364" s="33" t="n"/>
+      <c r="D364" s="33" t="n"/>
+      <c r="E364" s="33" t="n"/>
+      <c r="F364" s="33" t="n"/>
+    </row>
+    <row r="365" ht="30" customHeight="1">
+      <c r="A365" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 자주 확인하는 학원이 있다면 이름 두세 글자만 외워 두세요. 클릭 없이 바로 걸러집니다.</t>
+        </is>
+      </c>
+      <c r="B365" s="35" t="n"/>
+      <c r="C365" s="35" t="n"/>
+      <c r="D365" s="35" t="n"/>
+      <c r="E365" s="35" t="n"/>
+      <c r="F365" s="35" t="n"/>
+    </row>
+    <row r="367" ht="26" customHeight="1">
+      <c r="A367" s="21" t="inlineStr">
+        <is>
+          <t>29  💳 신규 결제 화면 단계형 개편  —  상품 12개를 한꺼번에 보여 주지 않아요</t>
+        </is>
+      </c>
+      <c r="B367" s="22" t="n"/>
+      <c r="C367" s="22" t="n"/>
+      <c r="D367" s="22" t="n"/>
+      <c r="E367" s="22" t="n"/>
+      <c r="F367" s="22" t="n"/>
+    </row>
+    <row r="368" ht="42" customHeight="1">
+      <c r="A368" s="23" t="inlineStr">
+        <is>
+          <t>📖 신규 결제 화면이 ‘대상 먼저 고르기’ 단계형으로 바뀌었습니다. 예전에는 첫 화면에 상품 12개가 한꺼번에 떠서 학부모가 무엇을 골라야 할지 막막했습니다. 이제 키즈 · 일반 1:1 · 그룹 · 비즈니스 · 시험 · 기업 중 대상을 먼저 고르면 해당 상품만 보입니다.</t>
+        </is>
+      </c>
+      <c r="B368" s="24" t="n"/>
+      <c r="C368" s="24" t="n"/>
+      <c r="D368" s="24" t="n"/>
+      <c r="E368" s="24" t="n"/>
+      <c r="F368" s="24" t="n"/>
+    </row>
+    <row r="369" ht="24" customHeight="1">
+      <c r="A369" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 신규 결제   ›   2 대상   ›   3 상품만   ›   4 전체 요금표 보기</t>
+        </is>
+      </c>
+      <c r="B369" s="26" t="n"/>
+      <c r="C369" s="26" t="n"/>
+      <c r="D369" s="26" t="n"/>
+      <c r="E369" s="26" t="n"/>
+      <c r="F369" s="26" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B370" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="30" customHeight="1">
+      <c r="A371" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B371" s="30" t="inlineStr">
+        <is>
+          <t>학부모에게 신규 결제 화면을 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="30" customHeight="1">
+      <c r="A372" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B372" s="30" t="inlineStr">
+        <is>
+          <t>대상(키즈·일반 1:1·그룹·비즈니스·시험·기업)을 먼저 고르게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="30" customHeight="1">
+      <c r="A373" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B373" s="30" t="inlineStr">
+        <is>
+          <t>고른 대상에 맞는 상품만 화면에 남아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="30" customHeight="1">
+      <c r="A374" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B374" s="30" t="inlineStr">
+        <is>
+          <t>전체를 비교하고 싶어 하면 전체 요금표 보기를 눌러 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="24" customHeight="1">
+      <c r="A375" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B375" s="32" t="inlineStr">
+        <is>
+          <t>상품 카드와 결제 로직은 하나도 바뀌지 않았어요 — 보여 주기만 나눈 것이라 안전합니다.</t>
+        </is>
+      </c>
+      <c r="C375" s="33" t="n"/>
+      <c r="D375" s="33" t="n"/>
+      <c r="E375" s="33" t="n"/>
+      <c r="F375" s="33" t="n"/>
+    </row>
+    <row r="376" ht="24" customHeight="1">
+      <c r="A376" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B376" s="32" t="inlineStr">
+        <is>
+          <t>초기 3개(무료체험·기타·규정) → 키즈 선택 시 4개 → 전체 12개로 확인됐습니다.</t>
+        </is>
+      </c>
+      <c r="C376" s="33" t="n"/>
+      <c r="D376" s="33" t="n"/>
+      <c r="E376" s="33" t="n"/>
+      <c r="F376" s="33" t="n"/>
+    </row>
+    <row r="377" ht="24" customHeight="1">
+      <c r="A377" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B377" s="32" t="inlineStr">
+        <is>
+          <t>전체 요금표 보기를 남겨 두었어요 — 가격을 숨긴다는 인상을 주면 역효과이기 때문입니다.</t>
+        </is>
+      </c>
+      <c r="C377" s="33" t="n"/>
+      <c r="D377" s="33" t="n"/>
+      <c r="E377" s="33" t="n"/>
+      <c r="F377" s="33" t="n"/>
+    </row>
+    <row r="378" ht="30" customHeight="1">
+      <c r="A378" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 전화에서 ‘어떤 걸 고를지 모르겠다’는 말이 나오면, 대상만 먼저 고르게 안내하세요.</t>
+        </is>
+      </c>
+      <c r="B378" s="35" t="n"/>
+      <c r="C378" s="35" t="n"/>
+      <c r="D378" s="35" t="n"/>
+      <c r="E378" s="35" t="n"/>
+      <c r="F378" s="35" t="n"/>
+    </row>
+    <row r="380" ht="26" customHeight="1">
+      <c r="A380" s="21" t="inlineStr">
+        <is>
+          <t>30  📋 계정 없는 학부모용 샘플 평가표  —  로그인 벽 앞에서 보여 줄 것이 생겼어요</t>
+        </is>
+      </c>
+      <c r="B380" s="22" t="n"/>
+      <c r="C380" s="22" t="n"/>
+      <c r="D380" s="22" t="n"/>
+      <c r="E380" s="22" t="n"/>
+      <c r="F380" s="22" t="n"/>
+    </row>
+    <row r="381" ht="42" customHeight="1">
+      <c r="A381" s="23" t="inlineStr">
+        <is>
+          <t>📖 계정이 없는 가망 학부모에게 보여 줄 것이 아무것도 없던 문제를 해결했습니다. 평가표 화면에 ‘계정이 없어요 — 샘플 평가표 먼저 보기’ 가 생겨, 로그인 없이 5축 점수 + 강사 코멘트 + AI 분석이 어떻게 나오는지 미리 보여 줄 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="B381" s="24" t="n"/>
+      <c r="C381" s="24" t="n"/>
+      <c r="D381" s="24" t="n"/>
+      <c r="E381" s="24" t="n"/>
+      <c r="F381" s="24" t="n"/>
+    </row>
+    <row r="382" ht="24" customHeight="1">
+      <c r="A382" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 평가표 화면   ›   2 계정이 없어요 — 샘플…   ›   3 5축 점수·강사 코멘트·…   ›   4 ‘우리 아이 것도 이렇게…</t>
+        </is>
+      </c>
+      <c r="B382" s="26" t="n"/>
+      <c r="C382" s="26" t="n"/>
+      <c r="D382" s="26" t="n"/>
+      <c r="E382" s="26" t="n"/>
+      <c r="F382" s="26" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B383" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="30" customHeight="1">
+      <c r="A384" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B384" s="30" t="inlineStr">
+        <is>
+          <t>상담 중 학부모에게 평가표 화면을 열어 보여 줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="30" customHeight="1">
+      <c r="A385" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B385" s="30" t="inlineStr">
+        <is>
+          <t>계정이 없어요 — 샘플 평가표 먼저 보기를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="30" customHeight="1">
+      <c r="A386" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B386" s="30" t="inlineStr">
+        <is>
+          <t>5축 점수·강사 코멘트·AI 분석 구성을 함께 보며 설명해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="30" customHeight="1">
+      <c r="A387" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B387" s="30" t="inlineStr">
+        <is>
+          <t>‘우리 아이 것도 이렇게 나옵니다’로 체험 신청을 연결해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="24" customHeight="1">
+      <c r="A388" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B388" s="32" t="inlineStr">
+        <is>
+          <t>⚠️ 값은 전부 예시입니다. 제목과 상단 배너에 ‘샘플/예시’ 표시가 들어가 있어요.</t>
+        </is>
+      </c>
+      <c r="C388" s="33" t="n"/>
+      <c r="D388" s="33" t="n"/>
+      <c r="E388" s="33" t="n"/>
+      <c r="F388" s="33" t="n"/>
+    </row>
+    <row r="389" ht="24" customHeight="1">
+      <c r="A389" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B389" s="32" t="inlineStr">
+        <is>
+          <t>이 표시는 절대 지우면 안 됩니다 — 실제 기록으로 오해되면 신뢰 문제가 됩니다.</t>
+        </is>
+      </c>
+      <c r="C389" s="33" t="n"/>
+      <c r="D389" s="33" t="n"/>
+      <c r="E389" s="33" t="n"/>
+      <c r="F389" s="33" t="n"/>
+    </row>
+    <row r="390" ht="26" customHeight="1">
+      <c r="A390" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 샘플은 실제 학생 데이터를 쓰지 않습니다. 상담 자료로만 활용하세요.</t>
+        </is>
+      </c>
+      <c r="B390" s="37" t="n"/>
+      <c r="C390" s="37" t="n"/>
+      <c r="D390" s="37" t="n"/>
+      <c r="E390" s="37" t="n"/>
+      <c r="F390" s="37" t="n"/>
+    </row>
+    <row r="391" ht="30" customHeight="1">
+      <c r="A391" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 첫 3분에 샘플 평가표를 보여 주면 ‘무엇을 받게 되는지’가 명확해져 체험 전환이 올라갑니다.</t>
+        </is>
+      </c>
+      <c r="B391" s="35" t="n"/>
+      <c r="C391" s="35" t="n"/>
+      <c r="D391" s="35" t="n"/>
+      <c r="E391" s="35" t="n"/>
+      <c r="F391" s="35" t="n"/>
+    </row>
+    <row r="393" ht="26" customHeight="1">
+      <c r="A393" s="21" t="inlineStr">
+        <is>
+          <t>31  📞 상담 창구·운영시간 통일 (카카오 1순위)  —  화면마다 달랐던 안내를 한 값으로</t>
+        </is>
+      </c>
+      <c r="B393" s="22" t="n"/>
+      <c r="C393" s="22" t="n"/>
+      <c r="D393" s="22" t="n"/>
+      <c r="E393" s="22" t="n"/>
+      <c r="F393" s="22" t="n"/>
+    </row>
+    <row r="394" ht="42" customHeight="1">
+      <c r="A394" s="23" t="inlineStr">
+        <is>
+          <t>📖 상담 운영시간이 화면마다 09-22 / 10-20 / 오후 7시로 제각각이던 문제를 10:00~23:00 (주말·공휴일 휴무) 한 값으로 통일했습니다. 또한 카카오 채널을 1순위 창구로 올리고, 전화 카드에도 ‘카카오가 더 빠릅니다’를 함께 표기했습니다.</t>
+        </is>
+      </c>
+      <c r="B394" s="24" t="n"/>
+      <c r="C394" s="24" t="n"/>
+      <c r="D394" s="24" t="n"/>
+      <c r="E394" s="24" t="n"/>
+      <c r="F394" s="24" t="n"/>
+    </row>
+    <row r="395" ht="24" customHeight="1">
+      <c r="A395" s="25" t="inlineStr">
+        <is>
+          <t>🧭  1 문의하기   ›   2 카카오 채널을 먼저   ›   3 10:00~23:00 (…</t>
+        </is>
+      </c>
+      <c r="B395" s="26" t="n"/>
+      <c r="C395" s="26" t="n"/>
+      <c r="D395" s="26" t="n"/>
+      <c r="E395" s="26" t="n"/>
+      <c r="F395" s="26" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="27" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B396" s="28" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="30" customHeight="1">
+      <c r="A397" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B397" s="30" t="inlineStr">
+        <is>
+          <t>문의하기 화면에서 카드 순서가 카카오 → 전화 인지 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="30" customHeight="1">
+      <c r="A398" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B398" s="30" t="inlineStr">
+        <is>
+          <t>학부모 안내 시 카카오 채널을 먼저 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="30" customHeight="1">
+      <c r="A399" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B399" s="30" t="inlineStr">
+        <is>
+          <t>운영시간은 10:00~23:00 (주말·공휴일 휴무) 로 통일해 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="24" customHeight="1">
+      <c r="A400" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B400" s="32" t="inlineStr">
+        <is>
+          <t>고친 곳: 문의 화면·홈 메뉴·FAQ(한/영)·AI 상담사 사실블록·학생 FAQ까지 전부 같은 값입니다.</t>
+        </is>
+      </c>
+      <c r="C400" s="33" t="n"/>
+      <c r="D400" s="33" t="n"/>
+      <c r="E400" s="33" t="n"/>
+      <c r="F400" s="33" t="n"/>
+    </row>
+    <row r="401" ht="24" customHeight="1">
+      <c r="A401" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B401" s="32" t="inlineStr">
+        <is>
+          <t>쓰지 않는 팩스 번호와 자리표시자 전화번호는 삭제했습니다.</t>
+        </is>
+      </c>
+      <c r="C401" s="33" t="n"/>
+      <c r="D401" s="33" t="n"/>
+      <c r="E401" s="33" t="n"/>
+      <c r="F401" s="33" t="n"/>
+    </row>
+    <row r="402" ht="24" customHeight="1">
+      <c r="A402" s="31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B402" s="32" t="inlineStr">
+        <is>
+          <t>AI 상담사도 같은 시간·같은 창구 순서로 안내합니다.</t>
+        </is>
+      </c>
+      <c r="C402" s="33" t="n"/>
+      <c r="D402" s="33" t="n"/>
+      <c r="E402" s="33" t="n"/>
+      <c r="F402" s="33" t="n"/>
+    </row>
+    <row r="403" ht="26" customHeight="1">
+      <c r="A403" s="36" t="inlineStr">
+        <is>
+          <t>알아두기 · 실제 운영시간이 바뀌면 이 값들을 한꺼번에 고쳐야 합니다. 한 곳만 고치면 다시 화면마다 달라집니다.</t>
+        </is>
+      </c>
+      <c r="B403" s="37" t="n"/>
+      <c r="C403" s="37" t="n"/>
+      <c r="D403" s="37" t="n"/>
+      <c r="E403" s="37" t="n"/>
+      <c r="F403" s="37" t="n"/>
+    </row>
+    <row r="404" ht="30" customHeight="1">
+      <c r="A404" s="34" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 필리핀 콜센터 번호가 필요하면 실번호를 알려 주세요 — 자리표시자였던 번호는 삭제된 상태입니다.</t>
+        </is>
+      </c>
+      <c r="B404" s="35" t="n"/>
+      <c r="C404" s="35" t="n"/>
+      <c r="D404" s="35" t="n"/>
+      <c r="E404" s="35" t="n"/>
+      <c r="F404" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="251">
+  <mergeCells count="362">
+    <mergeCell ref="B209:F209"/>
+    <mergeCell ref="B301:F301"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A369:F369"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="A394:F394"/>
+    <mergeCell ref="B276:F276"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B303:F303"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B278:F278"/>
+    <mergeCell ref="A280:F280"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="A340:F340"/>
+    <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B370:F370"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="B291:F291"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="A269:F269"/>
+    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="B322:F322"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B317:F317"/>
+    <mergeCell ref="B217:F217"/>
+    <mergeCell ref="B388:F388"/>
+    <mergeCell ref="B304:F304"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B375:F375"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B319:F319"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B383:F383"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="B401:F401"/>
+    <mergeCell ref="A390:F390"/>
+    <mergeCell ref="B272:F272"/>
+    <mergeCell ref="B259:F259"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B249:F249"/>
+    <mergeCell ref="B243:F243"/>
+    <mergeCell ref="B363:F363"/>
+    <mergeCell ref="A295:F295"/>
+    <mergeCell ref="B373:F373"/>
+    <mergeCell ref="A368:F368"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="B389:F389"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A378:F378"/>
+    <mergeCell ref="A365:F365"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B320:F320"/>
+    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="B247:F247"/>
+    <mergeCell ref="B385:F385"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="A298:F298"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A327:F327"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A391:F391"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B338:F338"/>
+    <mergeCell ref="A284:F284"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="B275:F275"/>
+    <mergeCell ref="B315:F315"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B302:F302"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B277:F277"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="B180:F180"/>
+    <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="B234:F234"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B270:F270"/>
+    <mergeCell ref="B257:F257"/>
+    <mergeCell ref="B288:F288"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="A228:F228"/>
+    <mergeCell ref="A355:F355"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B347:F347"/>
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="A254:F254"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A314:F314"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A216:F216"/>
+    <mergeCell ref="B359:F359"/>
+    <mergeCell ref="B207:F207"/>
+    <mergeCell ref="B204:F204"/>
+    <mergeCell ref="B271:F271"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A282:F282"/>
+    <mergeCell ref="B273:F273"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="A313:F313"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A342:F342"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A344:F344"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="B364:F364"/>
+    <mergeCell ref="A310:F310"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="A339:F339"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B286:F286"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A255:F255"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="B362:F362"/>
+    <mergeCell ref="B337:F337"/>
+    <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="A187:F187"/>
     <mergeCell ref="A174:F174"/>
-    <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A183:F183"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B129:F129"/>
     <mergeCell ref="B194:F194"/>
-    <mergeCell ref="B252:F252"/>
-    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B292:F292"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A238:F238"/>
     <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B236:F236"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B231:F231"/>
+    <mergeCell ref="B287:F287"/>
+    <mergeCell ref="B358:F358"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="B289:F289"/>
+    <mergeCell ref="A357:F357"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A329:F329"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B384:F384"/>
+    <mergeCell ref="B305:F305"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B386:F386"/>
+    <mergeCell ref="B208:F208"/>
+    <mergeCell ref="B219:F219"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="B210:F210"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="A215:F215"/>
+    <mergeCell ref="B318:F318"/>
+    <mergeCell ref="B333:F333"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
+    <mergeCell ref="B397:F397"/>
+    <mergeCell ref="B360:F360"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B372:F372"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="B374:F374"/>
+    <mergeCell ref="B361:F361"/>
+    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="B232:F232"/>
+    <mergeCell ref="B321:F321"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A381:F381"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="B323:F323"/>
+    <mergeCell ref="B244:F244"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="B387:F387"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B258:F258"/>
+    <mergeCell ref="B245:F245"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A300:F300"/>
+    <mergeCell ref="A343:F343"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B334:F334"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A264:F264"/>
+    <mergeCell ref="B165:F165"/>
+    <mergeCell ref="B336:F336"/>
+    <mergeCell ref="A356:F356"/>
+    <mergeCell ref="B400:F400"/>
+    <mergeCell ref="B402:F402"/>
+    <mergeCell ref="A380:F380"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="B377:F377"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A382:F382"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B316:F316"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B331:F331"/>
+    <mergeCell ref="B330:F330"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="B261:F261"/>
+    <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B214:F214"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B180:F180"/>
-    <mergeCell ref="B238:F238"/>
-    <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="A150:F150"/>
-    <mergeCell ref="B253:F253"/>
-    <mergeCell ref="B231:F231"/>
+    <mergeCell ref="A393:F393"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A159:F159"/>
-    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A395:F395"/>
     <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B250:F250"/>
     <mergeCell ref="B166:F166"/>
-    <mergeCell ref="A265:F265"/>
-    <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A274:F274"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B116:F116"/>
-    <mergeCell ref="A249:F249"/>
-    <mergeCell ref="B270:F270"/>
-    <mergeCell ref="B230:F230"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B168:F168"/>
-    <mergeCell ref="B257:F257"/>
-    <mergeCell ref="B84:F84"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="A186:F186"/>
-    <mergeCell ref="B92:F92"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="B241:F241"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B118:F118"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="B213:F213"/>
     <mergeCell ref="B256:F256"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="A250:F250"/>
-    <mergeCell ref="B135:F135"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="B242:F242"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="A237:F237"/>
+    <mergeCell ref="A212:F212"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A283:F283"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A236:F236"/>
-    <mergeCell ref="A149:F149"/>
     <mergeCell ref="B121:F121"/>
-    <mergeCell ref="A223:F223"/>
-    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="A214:F214"/>
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B167:F167"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="B219:F219"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B176:F176"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="A262:F262"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B266:F266"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B267:F267"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A199:F199"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="A127:F127"/>
-    <mergeCell ref="B217:F217"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="B269:F269"/>
-    <mergeCell ref="A232:F232"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B239:F239"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B254:F254"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B189:F189"/>
+    <mergeCell ref="B332:F332"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B396:F396"/>
+    <mergeCell ref="A230:F230"/>
+    <mergeCell ref="B398:F398"/>
+    <mergeCell ref="A403:F403"/>
+    <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A296:F296"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B204:F204"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B216:F216"/>
-    <mergeCell ref="B251:F251"/>
     <mergeCell ref="A162:F162"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B126:F126"/>
-    <mergeCell ref="B271:F271"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B218:F218"/>
-    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B345:F345"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="B59:F59"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B190:F190"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B202:F202"/>
-    <mergeCell ref="B215:F215"/>
-    <mergeCell ref="B273:F273"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A210:F210"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A129:F129"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B272:F272"/>
-    <mergeCell ref="B244:F244"/>
-    <mergeCell ref="B259:F259"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B229:F229"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B145:F145"/>
-    <mergeCell ref="A196:F196"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A171:F171"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A251:F251"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="B346:F346"/>
+    <mergeCell ref="A309:F309"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A253:F253"/>
+    <mergeCell ref="A324:F324"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B243:F243"/>
-    <mergeCell ref="B258:F258"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A173:F173"/>
-    <mergeCell ref="B245:F245"/>
-    <mergeCell ref="B255:F255"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B260:F260"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B201:F201"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B154:F154"/>
-    <mergeCell ref="B212:F212"/>
+    <mergeCell ref="A299:F299"/>
+    <mergeCell ref="B371:F371"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A353:F353"/>
+    <mergeCell ref="A328:F328"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B335:F335"/>
     <mergeCell ref="B206:F206"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B399:F399"/>
     <mergeCell ref="B203:F203"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="B237:F237"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="A246:F246"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="A264:F264"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="B165:F165"/>
-    <mergeCell ref="A233:F233"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A235:F235"/>
-    <mergeCell ref="A247:F247"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B151:F151"/>
-    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B117:F117"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A312:F312"/>
+    <mergeCell ref="A404:F404"/>
     <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A184:F184"/>
-    <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A170:F170"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B205:F205"/>
-    <mergeCell ref="A211:F211"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A220:F220"/>
-    <mergeCell ref="A130:F130"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A261:F261"/>
-    <mergeCell ref="A275:F275"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="A222:F222"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="A110:F110"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A119:F119"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A187:F187"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B268:F268"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B290:F290"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B348:F348"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="B285:F285"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A325:F325"/>
+    <mergeCell ref="A367:F367"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5294,7 +7761,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>확인 항목</t>
         </is>
@@ -5306,95 +7773,95 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>오늘 매출·재원·출석 지표를 확인했나요?</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr"/>
+      <c r="C4" s="41" t="inlineStr"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>신규 상담/문의를 접수·응대했나요?</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr"/>
+      <c r="C5" s="44" t="inlineStr"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>미납 건을 확인하고 안내했나요?</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr"/>
+      <c r="C6" s="41" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>이탈위험 학생을 챙겼나요?</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>학부모에게 리포트·마이페이지를 안내했나요?</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr"/>
+      <c r="C8" s="41" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>이번 달 정산(수령)을 확인했나요?</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr"/>
+      <c r="C9" s="44" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>체험→등록 후속 연락을 했나요?</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr"/>
+      <c r="C10" s="41" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5425,19 +7892,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>질문 (Q)</t>
         </is>
       </c>
-      <c r="B3" s="36" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>답변 (A)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>어디서 접속하나요?</t>
         </is>
@@ -5449,7 +7916,7 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>다른 대리점 데이터도 보이나요?</t>
         </is>
@@ -5461,7 +7928,7 @@
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>등록을 늘리려면?</t>
         </is>
@@ -5473,7 +7940,7 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>정산은 어떻게 확인하나요?</t>
         </is>
@@ -5485,7 +7952,7 @@
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>학생이 그만둘 것 같아요.</t>
         </is>
@@ -5525,130 +7992,130 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>재원생 추이(예시)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>1월</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="50" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="50" t="n">
         <v>135</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="50" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>4월</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="50" t="n">
         <v>162</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>5월</t>
         </is>
       </c>
-      <c r="B9" s="48" t="n">
+      <c r="B9" s="50" t="n">
         <v>171</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n">
+      <c r="B10" s="50" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>이탈위험 분포(예시)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="51" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>안전</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="29" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="29" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>위험</t>
         </is>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="29" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5675,21 +8142,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="50" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>🏁 마무리 · 대리점 성장을 위한 실천 가이드</t>
         </is>
       </c>
     </row>
     <row r="2" ht="54" customHeight="1">
-      <c r="A2" s="51" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>대리점 운영의 핵심은 ‘모객 → 등록 → 만족 → 재등록’의 선순환이에요. 상담을 빠르게 응대하고, 학습 성과를 데이터로 보여주고, 이탈을 미리 막으면 우리 대리점이 꾸준히 성장합니다. 이 리듬만 지켜도 운영이 든든해져요.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>🔄 하루 흐름 한눈에</t>
         </is>
@@ -5697,67 +8164,67 @@
       <c r="B4" s="22" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>아침 (5분)</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>대시보드에서 매출·재원·출석 확인, 실시간 수업 상태 점검</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>오전</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>신규 상담 응대·등록 전환, 미납 안내</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>수업 시간</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>수업 배정·진행 확인, ‘입장 문의’는 브라우저·권한부터 안내</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>오후</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>이탈위험 학생 케어, 학부모 리포트·상담</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>월간</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>지사→대리점 정산 확인, 재등록·후속 연락</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>⭐ 핵심 원칙</t>
         </is>
@@ -5765,113 +8232,113 @@
       <c r="B11" s="2" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>빠른 응대 — 상담·문의는 빠를수록 등록 전환율이 올라가요.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>데이터로 설득 — 학습 리포트로 성과를 보여주면 재등록이 쉬워요.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>이탈은 조기 개입 — 결석 잦은 학생부터 먼저 챙겨요.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>학부모와 소통 — 마이페이지·리포트로 신뢰를 쌓아요.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>후속 연락 — 상담 후 팔로업이 등록을 완성해요.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>📌 꼭 기억하세요</t>
         </is>
       </c>
-      <c r="B18" s="55" t="n"/>
+      <c r="B18" s="57" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>접속은 admin.mangoi.co.kr, 데이터는 우리 대리점 범위로 자동 한정돼요</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B20" s="57" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>정산은 지사→대리점 트리 구조로 자동 계산돼요</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B21" s="57" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>학생 ‘입장 안 됨’ 문의의 대부분은 브라우저·권한 문제예요</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="56" t="inlineStr">
+      <c r="A22" s="58" t="inlineStr">
         <is>
           <t>📌</t>
         </is>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>성장 리듬은 ‘모객 → 등록 → 만족 → 재등록’!</t>
         </is>
       </c>
     </row>
     <row r="24" ht="66" customHeight="1">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>🍊 대리점의 힘은 ‘내 학생 한 명 한 명을 챙기는 정성’에서 나와요. 빠르게 응대하고, 성과를 보여주고, 이탈을 미리 막으세요. 지사와 본사가 든든하게 지원합니다. 궁금한 점은 언제든 고객센터로 — 무럭무럭 성장하는 대리점을 응원합니다! 🍊</t>
         </is>
